--- a/model_maker/output/goodwe/stage1_goodwe.xlsx
+++ b/model_maker/output/goodwe/stage1_goodwe.xlsx
@@ -27,7 +27,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,10 +41,15 @@
       <sz val="9"/>
     </font>
     <font>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="9"/>
+    </font>
+    <font>
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -54,6 +59,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="002E75B6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E1F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -83,12 +93,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -456,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:L172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -535,8 +546,7402 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>--- Registers ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>0x0064</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Hz</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr"/>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" s="3" t="inlineStr"/>
+      <c r="J3" s="3" t="inlineStr"/>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>[4500, 6000]</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>0x0064</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Hz</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr"/>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" s="3" t="inlineStr"/>
+      <c r="J4" s="3" t="inlineStr"/>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>[5000, 6500]</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>0x0100</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>256</v>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Active power adjust</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>FC03/FC06</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" s="3" t="inlineStr"/>
+      <c r="J5" s="3" t="inlineStr"/>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>RW</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>0x0101</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>257</v>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>PF reactive power adjust</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>FC03/FC06</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" s="3" t="inlineStr"/>
+      <c r="J6" s="3" t="inlineStr"/>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>RW</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>0xFFFF</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>65535</v>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>1 % 1-20,lagging 0.99-0.8 80-100,leading 0.80-1, Note: if read command the inverter is not in PF setting mode (1547 use)</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr"/>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" s="3" t="inlineStr"/>
+      <c r="J7" s="3" t="inlineStr"/>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>[0, 0] | [1,20], [80,100]</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>0xFFFF</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>65535</v>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>% 1-20,lagging 0.99-0.8 80-100,leading 0.80-1, Note: if read command the inverter is not in PF setting mode (1547 use)</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr"/>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" s="3" t="inlineStr"/>
+      <c r="J8" s="3" t="inlineStr"/>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>[0, 0] | [1,20], [80,100]</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>0x0102</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>258</v>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Reactive power adjust</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>S32</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>FC03/FC06</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" s="3" t="inlineStr"/>
+      <c r="J9" s="3" t="inlineStr"/>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>RW</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>0x0104</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>260</v>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Max value of reactive power</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>U32</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" s="3" t="inlineStr"/>
+      <c r="J10" s="3" t="inlineStr"/>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>0x0106</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>262</v>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Export Power Limit Adjust</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>S16</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>FC06</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" s="3" t="inlineStr"/>
+      <c r="J11" s="3" t="inlineStr"/>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>0x0107</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>263</v>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>TaiWan Safety Vpset</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>FC03/FC06</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" s="3" t="inlineStr"/>
+      <c r="J12" s="3" t="inlineStr"/>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>RW</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>0x0108</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>264</v>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>TaiWan Safety PF adjust</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>FC03/FC06</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" s="3" t="inlineStr"/>
+      <c r="J13" s="3" t="inlineStr"/>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>RW</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>0x0064</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>% For Taiwan safety regulations (80-100)</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr"/>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" s="3" t="inlineStr"/>
+      <c r="J14" s="3" t="inlineStr"/>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>[80, 100]</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>0x0109</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>265</v>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>TaiWan Safety reactive power adjust</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>S16</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>FC03/FC06</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" s="3" t="inlineStr"/>
+      <c r="J15" s="3" t="inlineStr"/>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>RW</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>0x010A</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>266</v>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>TaiWan Safety active power adjust</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>FC03/FC06</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" s="3" t="inlineStr"/>
+      <c r="J16" s="3" t="inlineStr"/>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>RW</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>0x010B</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>267</v>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Export power limit Communication Overtime set</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>FC03/FC06</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" s="3" t="inlineStr"/>
+      <c r="J17" s="3" t="inlineStr"/>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>RW</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>0x010C</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>268</v>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>TaiWan VPC curve switch</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>FC03/FC06</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" s="3" t="inlineStr"/>
+      <c r="J18" s="3" t="inlineStr"/>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>RW</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>0x0120</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>288</v>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>Power On(Allow on grid self-test)</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>FC06</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" s="3" t="inlineStr"/>
+      <c r="J19" s="3" t="inlineStr"/>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>0x0121</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>289</v>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>Power Off(Not allow on grid self-test)</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>FC06</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" s="3" t="inlineStr"/>
+      <c r="J20" s="3" t="inlineStr"/>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>0x0122</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>290</v>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>Restart</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>FC06</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" s="3" t="inlineStr"/>
+      <c r="J21" s="3" t="inlineStr"/>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>0x0123</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>291</v>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>On Grid Export Power Limit Switch</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>FC03/FC06</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" s="3" t="inlineStr"/>
+      <c r="J22" s="3" t="inlineStr"/>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>RW</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>0x0124</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>292</v>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>Set the Export power percentage(Nee d to turn on the limit switch)</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>FC03/FC06</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" s="3" t="inlineStr"/>
+      <c r="J23" s="3" t="inlineStr"/>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>RW</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>0x0125</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>293</v>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Set the Export power percentage(No need to turn on the limit switch)</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>FC03/FC06</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" s="3" t="inlineStr"/>
+      <c r="J24" s="3" t="inlineStr"/>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>RW</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>0x0130</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>304</v>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Automatic Reactive power Adjust</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>FC06</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" s="3" t="inlineStr"/>
+      <c r="J25" s="3" t="inlineStr"/>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>0x0131</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>305</v>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>Automatic Reactive power Adjust ID</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>U32</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>FC06</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" s="3" t="inlineStr"/>
+      <c r="J26" s="3" t="inlineStr"/>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>0x0133</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>307</v>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>Battery Mode Switch(Brazil)</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>FC06</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" s="3" t="inlineStr"/>
+      <c r="J27" s="3" t="inlineStr"/>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>0x0134</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>308</v>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>Battery Voltage set(Brazil)</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>FC06</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" s="3" t="inlineStr"/>
+      <c r="J28" s="3" t="inlineStr"/>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>0x0138</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>312</v>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>Shadow mode switch</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>FC03/FC06</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" s="3" t="inlineStr"/>
+      <c r="J29" s="3" t="inlineStr"/>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>RW</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>0x0200</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>512</v>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>Device Serial</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>STR</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" s="3" t="inlineStr"/>
+      <c r="J30" s="3" t="inlineStr"/>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>0x0210</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>528</v>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>Device Type</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>STR</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I31" s="3" t="inlineStr"/>
+      <c r="J31" s="3" t="inlineStr"/>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>0x0220</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>544</v>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>Error Message</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>U32</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" s="3" t="inlineStr"/>
+      <c r="J32" s="3" t="inlineStr"/>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>0x0222</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>546</v>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>High Byte of Total Feed Power to grid /Total power generation</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I33" s="3" t="inlineStr"/>
+      <c r="J33" s="3" t="inlineStr"/>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>0x0223</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>547</v>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>Low Byte of Total Feed Power to grid/Total power generation</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I34" s="3" t="inlineStr"/>
+      <c r="J34" s="3" t="inlineStr"/>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>0x0224</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>548</v>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>High Byte of Total feeding hours/Hourly power generation</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" s="3" t="inlineStr"/>
+      <c r="J35" s="3" t="inlineStr"/>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>0x0225</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>549</v>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>Low Byte of Total feeding hours/Hourly power generation</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I36" s="3" t="inlineStr"/>
+      <c r="J36" s="3" t="inlineStr"/>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>0x0226</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>550</v>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>Vpv1 /PPV1 input voltage</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I37" s="3" t="inlineStr"/>
+      <c r="J37" s="3" t="inlineStr"/>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L37" s="3" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>0x0227</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>551</v>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>Vpv2 /PV2 input voltage</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I38" s="3" t="inlineStr"/>
+      <c r="J38" s="3" t="inlineStr"/>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="n">
+        <v>37</v>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>0x0228</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>552</v>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>Ipv1 /PV1 input current</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I39" s="3" t="inlineStr"/>
+      <c r="J39" s="3" t="inlineStr"/>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>0x0229</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>553</v>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>Ipv2 /PV2 input current</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I40" s="3" t="inlineStr"/>
+      <c r="J40" s="3" t="inlineStr"/>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>0x022A</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>554</v>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>Vac1 /L1 Phase voltage</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I41" s="3" t="inlineStr"/>
+      <c r="J41" s="3" t="inlineStr"/>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>0x022B</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>555</v>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>Vac2 /L2 Phase voltage</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I42" s="3" t="inlineStr"/>
+      <c r="J42" s="3" t="inlineStr"/>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="n">
+        <v>41</v>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>0x022C</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>556</v>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>Vac3 /L3 Phase voltage</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I43" s="3" t="inlineStr"/>
+      <c r="J43" s="3" t="inlineStr"/>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L43" s="3" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>0x022D</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>557</v>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>Iac1 /L1 Phase current</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I44" s="3" t="inlineStr"/>
+      <c r="J44" s="3" t="inlineStr"/>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="n">
+        <v>43</v>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>0x022E</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>558</v>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>Iac2 /L2 Phase current</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H45" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I45" s="3" t="inlineStr"/>
+      <c r="J45" s="3" t="inlineStr"/>
+      <c r="K45" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="n">
+        <v>44</v>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>0x022F</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>559</v>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>Iac3 /L3 Phase current</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I46" s="3" t="inlineStr"/>
+      <c r="J46" s="3" t="inlineStr"/>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>0x0230</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>560</v>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>Fac1 /L1 Phase frequency</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H47" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I47" s="3" t="inlineStr"/>
+      <c r="J47" s="3" t="inlineStr"/>
+      <c r="K47" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L47" s="3" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>0x0064</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>Hz Phase L1 frequency</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr"/>
+      <c r="G48" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H48" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I48" s="3" t="inlineStr"/>
+      <c r="J48" s="3" t="inlineStr"/>
+      <c r="K48" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L48" s="3" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>0x0231</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>561</v>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>Fac2 /L2 Phase frequency</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H49" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I49" s="3" t="inlineStr"/>
+      <c r="J49" s="3" t="inlineStr"/>
+      <c r="K49" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L49" s="3" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>0x0064</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>Hz Phase L2 frequency</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="inlineStr"/>
+      <c r="G50" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H50" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I50" s="3" t="inlineStr"/>
+      <c r="J50" s="3" t="inlineStr"/>
+      <c r="K50" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L50" s="3" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="n">
+        <v>49</v>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>0x0232</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>562</v>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>Fac3 /L3 Phase frequency</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="G51" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H51" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I51" s="3" t="inlineStr"/>
+      <c r="J51" s="3" t="inlineStr"/>
+      <c r="K51" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L51" s="3" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>0x0064</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>Hz Phase L3 frequency</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="inlineStr"/>
+      <c r="G52" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H52" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I52" s="3" t="inlineStr"/>
+      <c r="J52" s="3" t="inlineStr"/>
+      <c r="K52" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L52" s="3" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="n">
+        <v>51</v>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>0x0233</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>563</v>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>Pac L /Inverter current output power</t>
+        </is>
+      </c>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="G53" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H53" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I53" s="3" t="inlineStr"/>
+      <c r="J53" s="3" t="inlineStr"/>
+      <c r="K53" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L53" s="3" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="n">
+        <v>52</v>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>0x0234</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>564</v>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>Work Mode</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H54" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I54" s="3" t="inlineStr"/>
+      <c r="J54" s="3" t="inlineStr"/>
+      <c r="K54" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L54" s="3" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="n">
+        <v>53</v>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>0x0235</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="n">
+        <v>565</v>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>Inverter internal temperature</t>
+        </is>
+      </c>
+      <c r="F55" s="3" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="G55" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H55" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I55" s="3" t="inlineStr"/>
+      <c r="J55" s="3" t="inlineStr"/>
+      <c r="K55" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L55" s="3" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="n">
+        <v>54</v>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>0x0236</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>566</v>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>E-Day /Daily power generation</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="G56" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H56" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I56" s="3" t="inlineStr"/>
+      <c r="J56" s="3" t="inlineStr"/>
+      <c r="K56" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L56" s="3" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>0x0300</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>768</v>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>Vpv1 /PV1 input voltage</t>
+        </is>
+      </c>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="G57" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H57" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I57" s="3" t="inlineStr"/>
+      <c r="J57" s="3" t="inlineStr"/>
+      <c r="K57" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L57" s="3" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="n">
+        <v>56</v>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>0x0301</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>769</v>
+      </c>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>Vpv2 /PV2 input voltage</t>
+        </is>
+      </c>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="G58" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H58" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I58" s="3" t="inlineStr"/>
+      <c r="J58" s="3" t="inlineStr"/>
+      <c r="K58" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L58" s="3" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="n">
+        <v>57</v>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>0x0302</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>770</v>
+      </c>
+      <c r="E59" s="3" t="inlineStr">
+        <is>
+          <t>Ipv1 /PV1 input current</t>
+        </is>
+      </c>
+      <c r="F59" s="3" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="G59" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H59" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I59" s="3" t="inlineStr"/>
+      <c r="J59" s="3" t="inlineStr"/>
+      <c r="K59" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L59" s="3" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="n">
+        <v>58</v>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>0x0303</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>771</v>
+      </c>
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t>Ipv2 /PV2 input current</t>
+        </is>
+      </c>
+      <c r="F60" s="3" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="G60" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H60" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I60" s="3" t="inlineStr"/>
+      <c r="J60" s="3" t="inlineStr"/>
+      <c r="K60" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L60" s="3" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="n">
+        <v>59</v>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>0x0304</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>772</v>
+      </c>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>Vac1 /L1 Phase voltage</t>
+        </is>
+      </c>
+      <c r="F61" s="3" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="G61" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H61" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I61" s="3" t="inlineStr"/>
+      <c r="J61" s="3" t="inlineStr"/>
+      <c r="K61" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L61" s="3" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>0x0305</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>773</v>
+      </c>
+      <c r="E62" s="3" t="inlineStr">
+        <is>
+          <t>Vac2 /L2 Phase voltage</t>
+        </is>
+      </c>
+      <c r="F62" s="3" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="G62" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H62" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I62" s="3" t="inlineStr"/>
+      <c r="J62" s="3" t="inlineStr"/>
+      <c r="K62" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L62" s="3" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="n">
+        <v>61</v>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>0x0306</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="n">
+        <v>774</v>
+      </c>
+      <c r="E63" s="3" t="inlineStr">
+        <is>
+          <t>Vac3 /L3 Phase voltage</t>
+        </is>
+      </c>
+      <c r="F63" s="3" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="G63" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H63" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I63" s="3" t="inlineStr"/>
+      <c r="J63" s="3" t="inlineStr"/>
+      <c r="K63" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L63" s="3" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="n">
+        <v>62</v>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>0x0307</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>775</v>
+      </c>
+      <c r="E64" s="3" t="inlineStr">
+        <is>
+          <t>Iac1 /L1 Phase current</t>
+        </is>
+      </c>
+      <c r="F64" s="3" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="G64" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H64" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I64" s="3" t="inlineStr"/>
+      <c r="J64" s="3" t="inlineStr"/>
+      <c r="K64" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L64" s="3" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>0x0308</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>776</v>
+      </c>
+      <c r="E65" s="3" t="inlineStr">
+        <is>
+          <t>Iac2 /L2 Phase current</t>
+        </is>
+      </c>
+      <c r="F65" s="3" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="G65" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H65" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I65" s="3" t="inlineStr"/>
+      <c r="J65" s="3" t="inlineStr"/>
+      <c r="K65" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L65" s="3" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="n">
+        <v>64</v>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>0x0309</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>777</v>
+      </c>
+      <c r="E66" s="3" t="inlineStr">
+        <is>
+          <t>Iac3 /L3 Phase current</t>
+        </is>
+      </c>
+      <c r="F66" s="3" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="G66" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H66" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I66" s="3" t="inlineStr"/>
+      <c r="J66" s="3" t="inlineStr"/>
+      <c r="K66" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L66" s="3" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t>0x030A</t>
+        </is>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>778</v>
+      </c>
+      <c r="E67" s="3" t="inlineStr">
+        <is>
+          <t>Fac1 /L1 Phase frequency</t>
+        </is>
+      </c>
+      <c r="F67" s="3" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="G67" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H67" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I67" s="3" t="inlineStr"/>
+      <c r="J67" s="3" t="inlineStr"/>
+      <c r="K67" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L67" s="3" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>0x0064</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="E68" s="3" t="inlineStr">
+        <is>
+          <t>Hz Phase L1 frequency</t>
+        </is>
+      </c>
+      <c r="F68" s="3" t="inlineStr"/>
+      <c r="G68" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H68" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I68" s="3" t="inlineStr"/>
+      <c r="J68" s="3" t="inlineStr"/>
+      <c r="K68" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L68" s="3" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="n">
+        <v>67</v>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>0x030B</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="n">
+        <v>779</v>
+      </c>
+      <c r="E69" s="3" t="inlineStr">
+        <is>
+          <t>Fac2 /L2 Phase frequency</t>
+        </is>
+      </c>
+      <c r="F69" s="3" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="G69" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H69" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I69" s="3" t="inlineStr"/>
+      <c r="J69" s="3" t="inlineStr"/>
+      <c r="K69" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L69" s="3" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="n">
+        <v>68</v>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>0x0064</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="E70" s="3" t="inlineStr">
+        <is>
+          <t>Hz Phase L2 frequency</t>
+        </is>
+      </c>
+      <c r="F70" s="3" t="inlineStr"/>
+      <c r="G70" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H70" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I70" s="3" t="inlineStr"/>
+      <c r="J70" s="3" t="inlineStr"/>
+      <c r="K70" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L70" s="3" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="n">
+        <v>69</v>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>0x030C</t>
+        </is>
+      </c>
+      <c r="D71" s="3" t="n">
+        <v>780</v>
+      </c>
+      <c r="E71" s="3" t="inlineStr">
+        <is>
+          <t>Fac3 /L3 Phase frequency</t>
+        </is>
+      </c>
+      <c r="F71" s="3" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="G71" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H71" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I71" s="3" t="inlineStr"/>
+      <c r="J71" s="3" t="inlineStr"/>
+      <c r="K71" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L71" s="3" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="n">
+        <v>70</v>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>0x0064</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="E72" s="3" t="inlineStr">
+        <is>
+          <t>Hz Phase L3 frequency</t>
+        </is>
+      </c>
+      <c r="F72" s="3" t="inlineStr"/>
+      <c r="G72" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H72" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I72" s="3" t="inlineStr"/>
+      <c r="J72" s="3" t="inlineStr"/>
+      <c r="K72" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L72" s="3" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="n">
+        <v>71</v>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>0x030D</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="n">
+        <v>781</v>
+      </c>
+      <c r="E73" s="3" t="inlineStr">
+        <is>
+          <t>Pac L /Inverter current output power</t>
+        </is>
+      </c>
+      <c r="F73" s="3" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="G73" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H73" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I73" s="3" t="inlineStr"/>
+      <c r="J73" s="3" t="inlineStr"/>
+      <c r="K73" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L73" s="3" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="n">
+        <v>72</v>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>0x030E</t>
+        </is>
+      </c>
+      <c r="D74" s="3" t="n">
+        <v>782</v>
+      </c>
+      <c r="E74" s="3" t="inlineStr">
+        <is>
+          <t>Work Mode</t>
+        </is>
+      </c>
+      <c r="F74" s="3" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="G74" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H74" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I74" s="3" t="inlineStr"/>
+      <c r="J74" s="3" t="inlineStr"/>
+      <c r="K74" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L74" s="3" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="n">
+        <v>73</v>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t>0x030F</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="n">
+        <v>783</v>
+      </c>
+      <c r="E75" s="3" t="inlineStr">
+        <is>
+          <t>Inverter internal temperature</t>
+        </is>
+      </c>
+      <c r="F75" s="3" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="G75" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H75" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I75" s="3" t="inlineStr"/>
+      <c r="J75" s="3" t="inlineStr"/>
+      <c r="K75" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L75" s="3" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="n">
+        <v>74</v>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>0x0310</t>
+        </is>
+      </c>
+      <c r="D76" s="3" t="n">
+        <v>784</v>
+      </c>
+      <c r="E76" s="3" t="inlineStr">
+        <is>
+          <t>Error Message H</t>
+        </is>
+      </c>
+      <c r="F76" s="3" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="G76" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H76" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I76" s="3" t="inlineStr"/>
+      <c r="J76" s="3" t="inlineStr"/>
+      <c r="K76" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L76" s="3" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="n">
+        <v>75</v>
+      </c>
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t>0x0311</t>
+        </is>
+      </c>
+      <c r="D77" s="3" t="n">
+        <v>785</v>
+      </c>
+      <c r="E77" s="3" t="inlineStr">
+        <is>
+          <t>Error Message L</t>
+        </is>
+      </c>
+      <c r="F77" s="3" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="G77" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H77" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I77" s="3" t="inlineStr"/>
+      <c r="J77" s="3" t="inlineStr"/>
+      <c r="K77" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L77" s="3" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t>0x0312</t>
+        </is>
+      </c>
+      <c r="D78" s="3" t="n">
+        <v>786</v>
+      </c>
+      <c r="E78" s="3" t="inlineStr">
+        <is>
+          <t>High Byte of Total Feed Power to grid/Total power generation</t>
+        </is>
+      </c>
+      <c r="F78" s="3" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="G78" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H78" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I78" s="3" t="inlineStr"/>
+      <c r="J78" s="3" t="inlineStr"/>
+      <c r="K78" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L78" s="3" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="n">
+        <v>77</v>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="inlineStr">
+        <is>
+          <t>0x0313</t>
+        </is>
+      </c>
+      <c r="D79" s="3" t="n">
+        <v>787</v>
+      </c>
+      <c r="E79" s="3" t="inlineStr">
+        <is>
+          <t>Low Byte of Total Feed Power to grid/Total power generation</t>
+        </is>
+      </c>
+      <c r="F79" s="3" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="G79" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H79" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I79" s="3" t="inlineStr"/>
+      <c r="J79" s="3" t="inlineStr"/>
+      <c r="K79" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L79" s="3" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="n">
+        <v>78</v>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="inlineStr">
+        <is>
+          <t>0x0314</t>
+        </is>
+      </c>
+      <c r="D80" s="3" t="n">
+        <v>788</v>
+      </c>
+      <c r="E80" s="3" t="inlineStr">
+        <is>
+          <t>High Byte of Total feeding hours/Hourly power generation</t>
+        </is>
+      </c>
+      <c r="F80" s="3" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="G80" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H80" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I80" s="3" t="inlineStr"/>
+      <c r="J80" s="3" t="inlineStr"/>
+      <c r="K80" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L80" s="3" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="n">
+        <v>79</v>
+      </c>
+      <c r="B81" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C81" s="3" t="inlineStr">
+        <is>
+          <t>0x0315</t>
+        </is>
+      </c>
+      <c r="D81" s="3" t="n">
+        <v>789</v>
+      </c>
+      <c r="E81" s="3" t="inlineStr">
+        <is>
+          <t>Low Byte of Total feeding hours/Hourly power generation</t>
+        </is>
+      </c>
+      <c r="F81" s="3" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="G81" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H81" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I81" s="3" t="inlineStr"/>
+      <c r="J81" s="3" t="inlineStr"/>
+      <c r="K81" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L81" s="3" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C82" s="3" t="inlineStr">
+        <is>
+          <t>0x0316</t>
+        </is>
+      </c>
+      <c r="D82" s="3" t="n">
+        <v>790</v>
+      </c>
+      <c r="E82" s="3" t="inlineStr">
+        <is>
+          <t>Firmware Version</t>
+        </is>
+      </c>
+      <c r="F82" s="3" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="G82" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H82" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I82" s="3" t="inlineStr"/>
+      <c r="J82" s="3" t="inlineStr"/>
+      <c r="K82" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L82" s="3" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="3" t="n">
+        <v>81</v>
+      </c>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="inlineStr">
+        <is>
+          <t>0x0317</t>
+        </is>
+      </c>
+      <c r="D83" s="3" t="n">
+        <v>791</v>
+      </c>
+      <c r="E83" s="3" t="inlineStr">
+        <is>
+          <t>Warning Code</t>
+        </is>
+      </c>
+      <c r="F83" s="3" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="G83" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H83" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I83" s="3" t="inlineStr"/>
+      <c r="J83" s="3" t="inlineStr"/>
+      <c r="K83" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L83" s="3" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="3" t="n">
+        <v>82</v>
+      </c>
+      <c r="B84" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C84" s="3" t="inlineStr">
+        <is>
+          <t>0x0318</t>
+        </is>
+      </c>
+      <c r="D84" s="3" t="n">
+        <v>792</v>
+      </c>
+      <c r="E84" s="3" t="inlineStr">
+        <is>
+          <t>RSVD</t>
+        </is>
+      </c>
+      <c r="F84" s="3" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="G84" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H84" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I84" s="3" t="inlineStr"/>
+      <c r="J84" s="3" t="inlineStr"/>
+      <c r="K84" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L84" s="3" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="3" t="n">
+        <v>83</v>
+      </c>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C85" s="3" t="inlineStr">
+        <is>
+          <t>0x0319</t>
+        </is>
+      </c>
+      <c r="D85" s="3" t="n">
+        <v>793</v>
+      </c>
+      <c r="E85" s="3" t="inlineStr">
+        <is>
+          <t>Function Status Bits</t>
+        </is>
+      </c>
+      <c r="F85" s="3" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="G85" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H85" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I85" s="3" t="inlineStr"/>
+      <c r="J85" s="3" t="inlineStr"/>
+      <c r="K85" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L85" s="3" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="3" t="n">
+        <v>84</v>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C86" s="3" t="inlineStr">
+        <is>
+          <t>0x031A</t>
+        </is>
+      </c>
+      <c r="D86" s="3" t="n">
+        <v>794</v>
+      </c>
+      <c r="E86" s="3" t="inlineStr">
+        <is>
+          <t>RSVD</t>
+        </is>
+      </c>
+      <c r="F86" s="3" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="G86" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H86" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I86" s="3" t="inlineStr"/>
+      <c r="J86" s="3" t="inlineStr"/>
+      <c r="K86" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L86" s="3" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="3" t="n">
+        <v>85</v>
+      </c>
+      <c r="B87" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C87" s="3" t="inlineStr">
+        <is>
+          <t>0x031B</t>
+        </is>
+      </c>
+      <c r="D87" s="3" t="n">
+        <v>795</v>
+      </c>
+      <c r="E87" s="3" t="inlineStr">
+        <is>
+          <t>RSVD</t>
+        </is>
+      </c>
+      <c r="F87" s="3" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="G87" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H87" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I87" s="3" t="inlineStr"/>
+      <c r="J87" s="3" t="inlineStr"/>
+      <c r="K87" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L87" s="3" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="3" t="n">
+        <v>86</v>
+      </c>
+      <c r="B88" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C88" s="3" t="inlineStr">
+        <is>
+          <t>0x031C</t>
+        </is>
+      </c>
+      <c r="D88" s="3" t="n">
+        <v>796</v>
+      </c>
+      <c r="E88" s="3" t="inlineStr">
+        <is>
+          <t>BUS Voltage</t>
+        </is>
+      </c>
+      <c r="F88" s="3" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="G88" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H88" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I88" s="3" t="inlineStr"/>
+      <c r="J88" s="3" t="inlineStr"/>
+      <c r="K88" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L88" s="3" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="3" t="n">
+        <v>87</v>
+      </c>
+      <c r="B89" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C89" s="3" t="inlineStr">
+        <is>
+          <t>0x031D</t>
+        </is>
+      </c>
+      <c r="D89" s="3" t="n">
+        <v>797</v>
+      </c>
+      <c r="E89" s="3" t="inlineStr">
+        <is>
+          <t>NBUS Voltage</t>
+        </is>
+      </c>
+      <c r="F89" s="3" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="G89" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H89" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I89" s="3" t="inlineStr"/>
+      <c r="J89" s="3" t="inlineStr"/>
+      <c r="K89" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L89" s="3" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="3" t="n">
+        <v>88</v>
+      </c>
+      <c r="B90" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C90" s="3" t="inlineStr">
+        <is>
+          <t>0x031E</t>
+        </is>
+      </c>
+      <c r="D90" s="3" t="n">
+        <v>798</v>
+      </c>
+      <c r="E90" s="3" t="inlineStr">
+        <is>
+          <t>RSVD</t>
+        </is>
+      </c>
+      <c r="F90" s="3" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="G90" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H90" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I90" s="3" t="inlineStr"/>
+      <c r="J90" s="3" t="inlineStr"/>
+      <c r="K90" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L90" s="3" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="3" t="n">
+        <v>89</v>
+      </c>
+      <c r="B91" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C91" s="3" t="inlineStr">
+        <is>
+          <t>0x0064</t>
+        </is>
+      </c>
+      <c r="D91" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="E91" s="3" t="inlineStr">
+        <is>
+          <t>Hz RSVD</t>
+        </is>
+      </c>
+      <c r="F91" s="3" t="inlineStr"/>
+      <c r="G91" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H91" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I91" s="3" t="inlineStr"/>
+      <c r="J91" s="3" t="inlineStr"/>
+      <c r="K91" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L91" s="3" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="B92" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C92" s="3" t="inlineStr">
+        <is>
+          <t>0x031F</t>
+        </is>
+      </c>
+      <c r="D92" s="3" t="n">
+        <v>799</v>
+      </c>
+      <c r="E92" s="3" t="inlineStr">
+        <is>
+          <t>Safety Code</t>
+        </is>
+      </c>
+      <c r="F92" s="3" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="G92" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H92" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I92" s="3" t="inlineStr"/>
+      <c r="J92" s="3" t="inlineStr"/>
+      <c r="K92" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L92" s="3" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="3" t="n">
+        <v>91</v>
+      </c>
+      <c r="B93" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C93" s="3" t="inlineStr">
+        <is>
+          <t>0x0320</t>
+        </is>
+      </c>
+      <c r="D93" s="3" t="n">
+        <v>800</v>
+      </c>
+      <c r="E93" s="3" t="inlineStr">
+        <is>
+          <t>Feed Power to grid in today/ Daily power</t>
+        </is>
+      </c>
+      <c r="F93" s="3" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="G93" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H93" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I93" s="3" t="inlineStr"/>
+      <c r="J93" s="3" t="inlineStr"/>
+      <c r="K93" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L93" s="3" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="3" t="n">
+        <v>92</v>
+      </c>
+      <c r="B94" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C94" s="3" t="inlineStr">
+        <is>
+          <t>0x0324</t>
+        </is>
+      </c>
+      <c r="D94" s="3" t="n">
+        <v>804</v>
+      </c>
+      <c r="E94" s="3" t="inlineStr">
+        <is>
+          <t>Vpv5 /PV5 input voltage</t>
+        </is>
+      </c>
+      <c r="F94" s="3" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="G94" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H94" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I94" s="3" t="inlineStr"/>
+      <c r="J94" s="3" t="inlineStr"/>
+      <c r="K94" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L94" s="3" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="3" t="n">
+        <v>93</v>
+      </c>
+      <c r="B95" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C95" s="3" t="inlineStr">
+        <is>
+          <t>0x0325</t>
+        </is>
+      </c>
+      <c r="D95" s="3" t="n">
+        <v>805</v>
+      </c>
+      <c r="E95" s="3" t="inlineStr">
+        <is>
+          <t>Ipv5 /PV5 input current</t>
+        </is>
+      </c>
+      <c r="F95" s="3" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="G95" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H95" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I95" s="3" t="inlineStr"/>
+      <c r="J95" s="3" t="inlineStr"/>
+      <c r="K95" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L95" s="3" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="3" t="n">
+        <v>94</v>
+      </c>
+      <c r="B96" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C96" s="3" t="inlineStr">
+        <is>
+          <t>0x0326</t>
+        </is>
+      </c>
+      <c r="D96" s="3" t="n">
+        <v>806</v>
+      </c>
+      <c r="E96" s="3" t="inlineStr">
+        <is>
+          <t>Vpv6 /PV6 input voltage</t>
+        </is>
+      </c>
+      <c r="F96" s="3" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="G96" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H96" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I96" s="3" t="inlineStr"/>
+      <c r="J96" s="3" t="inlineStr"/>
+      <c r="K96" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L96" s="3" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="B97" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C97" s="3" t="inlineStr">
+        <is>
+          <t>0x0327</t>
+        </is>
+      </c>
+      <c r="D97" s="3" t="n">
+        <v>807</v>
+      </c>
+      <c r="E97" s="3" t="inlineStr">
+        <is>
+          <t>Ipv6 /PV6 input current</t>
+        </is>
+      </c>
+      <c r="F97" s="3" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="G97" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H97" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I97" s="3" t="inlineStr"/>
+      <c r="J97" s="3" t="inlineStr"/>
+      <c r="K97" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L97" s="3" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="3" t="n">
+        <v>96</v>
+      </c>
+      <c r="B98" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C98" s="3" t="inlineStr">
+        <is>
+          <t>0x033B</t>
+        </is>
+      </c>
+      <c r="D98" s="3" t="n">
+        <v>827</v>
+      </c>
+      <c r="E98" s="3" t="inlineStr">
+        <is>
+          <t>Year :Month</t>
+        </is>
+      </c>
+      <c r="F98" s="3" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="G98" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H98" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I98" s="3" t="inlineStr"/>
+      <c r="J98" s="3" t="inlineStr"/>
+      <c r="K98" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L98" s="3" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="3" t="n">
+        <v>97</v>
+      </c>
+      <c r="B99" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C99" s="3" t="inlineStr">
+        <is>
+          <t>0x033C</t>
+        </is>
+      </c>
+      <c r="D99" s="3" t="n">
+        <v>828</v>
+      </c>
+      <c r="E99" s="3" t="inlineStr">
+        <is>
+          <t>Date :Hour</t>
+        </is>
+      </c>
+      <c r="F99" s="3" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="G99" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H99" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I99" s="3" t="inlineStr"/>
+      <c r="J99" s="3" t="inlineStr"/>
+      <c r="K99" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L99" s="3" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="B100" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C100" s="3" t="inlineStr">
+        <is>
+          <t>0x033D</t>
+        </is>
+      </c>
+      <c r="D100" s="3" t="n">
+        <v>829</v>
+      </c>
+      <c r="E100" s="3" t="inlineStr">
+        <is>
+          <t>Minute :Second</t>
+        </is>
+      </c>
+      <c r="F100" s="3" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="G100" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H100" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I100" s="3" t="inlineStr"/>
+      <c r="J100" s="3" t="inlineStr"/>
+      <c r="K100" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L100" s="3" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="3" t="n">
+        <v>99</v>
+      </c>
+      <c r="B101" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C101" s="3" t="inlineStr">
+        <is>
+          <t>0x033E</t>
+        </is>
+      </c>
+      <c r="D101" s="3" t="n">
+        <v>830</v>
+      </c>
+      <c r="E101" s="3" t="inlineStr">
+        <is>
+          <t>Manufacture ID</t>
+        </is>
+      </c>
+      <c r="F101" s="3" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="G101" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H101" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I101" s="3" t="inlineStr"/>
+      <c r="J101" s="3" t="inlineStr"/>
+      <c r="K101" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L101" s="3" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="B102" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C102" s="3" t="inlineStr">
+        <is>
+          <t>0x033F</t>
+        </is>
+      </c>
+      <c r="D102" s="3" t="n">
+        <v>831</v>
+      </c>
+      <c r="E102" s="3" t="inlineStr">
+        <is>
+          <t>Wireless signal strength</t>
+        </is>
+      </c>
+      <c r="F102" s="3" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="G102" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H102" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I102" s="3" t="inlineStr"/>
+      <c r="J102" s="3" t="inlineStr"/>
+      <c r="K102" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L102" s="3" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="3" t="n">
+        <v>101</v>
+      </c>
+      <c r="B103" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C103" s="3" t="inlineStr">
+        <is>
+          <t>0x0340</t>
+        </is>
+      </c>
+      <c r="D103" s="3" t="n">
+        <v>832</v>
+      </c>
+      <c r="E103" s="3" t="inlineStr">
+        <is>
+          <t>High Byte of PV Mode（SMT only）</t>
+        </is>
+      </c>
+      <c r="F103" s="3" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="G103" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H103" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I103" s="3" t="inlineStr"/>
+      <c r="J103" s="3" t="inlineStr"/>
+      <c r="K103" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L103" s="3" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="3" t="n">
+        <v>102</v>
+      </c>
+      <c r="B104" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C104" s="3" t="inlineStr">
+        <is>
+          <t>0x0341</t>
+        </is>
+      </c>
+      <c r="D104" s="3" t="n">
+        <v>833</v>
+      </c>
+      <c r="E104" s="3" t="inlineStr">
+        <is>
+          <t>Low Byte of PV Mode（SMT only）</t>
+        </is>
+      </c>
+      <c r="F104" s="3" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="G104" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H104" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I104" s="3" t="inlineStr"/>
+      <c r="J104" s="3" t="inlineStr"/>
+      <c r="K104" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L104" s="3" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="3" t="n">
+        <v>103</v>
+      </c>
+      <c r="B105" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C105" s="3" t="inlineStr">
+        <is>
+          <t>0x0352</t>
+        </is>
+      </c>
+      <c r="D105" s="3" t="n">
+        <v>850</v>
+      </c>
+      <c r="E105" s="3" t="inlineStr">
+        <is>
+          <t>High Byte of Power</t>
+        </is>
+      </c>
+      <c r="F105" s="3" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="G105" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H105" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I105" s="3" t="inlineStr"/>
+      <c r="J105" s="3" t="inlineStr"/>
+      <c r="K105" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L105" s="3" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="3" t="n">
+        <v>104</v>
+      </c>
+      <c r="B106" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C106" s="3" t="inlineStr">
+        <is>
+          <t>0x0353</t>
+        </is>
+      </c>
+      <c r="D106" s="3" t="n">
+        <v>851</v>
+      </c>
+      <c r="E106" s="3" t="inlineStr">
+        <is>
+          <t>Low Byte of Power</t>
+        </is>
+      </c>
+      <c r="F106" s="3" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="G106" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H106" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I106" s="3" t="inlineStr"/>
+      <c r="J106" s="3" t="inlineStr"/>
+      <c r="K106" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L106" s="3" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="3" t="n">
+        <v>105</v>
+      </c>
+      <c r="B107" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C107" s="3" t="inlineStr">
+        <is>
+          <t>0x0354</t>
+        </is>
+      </c>
+      <c r="D107" s="3" t="n">
+        <v>852</v>
+      </c>
+      <c r="E107" s="3" t="inlineStr">
+        <is>
+          <t>Firmware Version of ARM</t>
+        </is>
+      </c>
+      <c r="F107" s="3" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="G107" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H107" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I107" s="3" t="inlineStr"/>
+      <c r="J107" s="3" t="inlineStr"/>
+      <c r="K107" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L107" s="3" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="3" t="n">
+        <v>106</v>
+      </c>
+      <c r="B108" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C108" s="3" t="inlineStr">
+        <is>
+          <t>0x0355</t>
+        </is>
+      </c>
+      <c r="D108" s="3" t="n">
+        <v>853</v>
+      </c>
+      <c r="E108" s="3" t="inlineStr">
+        <is>
+          <t>GPRS Burn-in Mode</t>
+        </is>
+      </c>
+      <c r="F108" s="3" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="G108" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H108" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I108" s="3" t="inlineStr"/>
+      <c r="J108" s="3" t="inlineStr"/>
+      <c r="K108" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L108" s="3" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="3" t="n">
+        <v>107</v>
+      </c>
+      <c r="B109" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C109" s="3" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="D109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E109" s="3" t="inlineStr">
+        <is>
+          <t>1 NA</t>
+        </is>
+      </c>
+      <c r="F109" s="3" t="inlineStr"/>
+      <c r="G109" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H109" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I109" s="3" t="inlineStr"/>
+      <c r="J109" s="3" t="inlineStr"/>
+      <c r="K109" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L109" s="3" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="3" t="n">
+        <v>108</v>
+      </c>
+      <c r="B110" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C110" s="3" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="D110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E110" s="3" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F110" s="3" t="inlineStr"/>
+      <c r="G110" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H110" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I110" s="3" t="inlineStr"/>
+      <c r="J110" s="3" t="inlineStr"/>
+      <c r="K110" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L110" s="3" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="3" t="n">
+        <v>109</v>
+      </c>
+      <c r="B111" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C111" s="3" t="inlineStr">
+        <is>
+          <t>0x0356</t>
+        </is>
+      </c>
+      <c r="D111" s="3" t="n">
+        <v>854</v>
+      </c>
+      <c r="E111" s="3" t="inlineStr">
+        <is>
+          <t>Pac H /High Byte of Power</t>
+        </is>
+      </c>
+      <c r="F111" s="3" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="G111" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H111" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I111" s="3" t="inlineStr"/>
+      <c r="J111" s="3" t="inlineStr"/>
+      <c r="K111" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L111" s="3" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="3" t="n">
+        <v>110</v>
+      </c>
+      <c r="B112" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C112" s="3" t="inlineStr">
+        <is>
+          <t>0x0357</t>
+        </is>
+      </c>
+      <c r="D112" s="3" t="n">
+        <v>855</v>
+      </c>
+      <c r="E112" s="3" t="inlineStr">
+        <is>
+          <t>Vpv3 /PV3 input voltage</t>
+        </is>
+      </c>
+      <c r="F112" s="3" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="G112" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H112" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I112" s="3" t="inlineStr"/>
+      <c r="J112" s="3" t="inlineStr"/>
+      <c r="K112" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L112" s="3" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="3" t="n">
+        <v>111</v>
+      </c>
+      <c r="B113" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C113" s="3" t="inlineStr">
+        <is>
+          <t>0x0358</t>
+        </is>
+      </c>
+      <c r="D113" s="3" t="n">
+        <v>856</v>
+      </c>
+      <c r="E113" s="3" t="inlineStr">
+        <is>
+          <t>Vpv4 /PV4 input voltage</t>
+        </is>
+      </c>
+      <c r="F113" s="3" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="G113" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H113" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I113" s="3" t="inlineStr"/>
+      <c r="J113" s="3" t="inlineStr"/>
+      <c r="K113" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L113" s="3" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="3" t="n">
+        <v>112</v>
+      </c>
+      <c r="B114" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C114" s="3" t="inlineStr">
+        <is>
+          <t>0x0359</t>
+        </is>
+      </c>
+      <c r="D114" s="3" t="n">
+        <v>857</v>
+      </c>
+      <c r="E114" s="3" t="inlineStr">
+        <is>
+          <t>Ipv3 /PV3 input current</t>
+        </is>
+      </c>
+      <c r="F114" s="3" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="G114" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H114" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I114" s="3" t="inlineStr"/>
+      <c r="J114" s="3" t="inlineStr"/>
+      <c r="K114" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L114" s="3" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="3" t="n">
+        <v>113</v>
+      </c>
+      <c r="B115" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C115" s="3" t="inlineStr">
+        <is>
+          <t>0x035A</t>
+        </is>
+      </c>
+      <c r="D115" s="3" t="n">
+        <v>858</v>
+      </c>
+      <c r="E115" s="3" t="inlineStr">
+        <is>
+          <t>Ipv4 /PV4 input current</t>
+        </is>
+      </c>
+      <c r="F115" s="3" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="G115" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H115" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I115" s="3" t="inlineStr"/>
+      <c r="J115" s="3" t="inlineStr"/>
+      <c r="K115" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L115" s="3" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="B116" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C116" s="3" t="inlineStr">
+        <is>
+          <t>0x035B</t>
+        </is>
+      </c>
+      <c r="D116" s="3" t="n">
+        <v>859</v>
+      </c>
+      <c r="E116" s="3" t="inlineStr">
+        <is>
+          <t>Istr1/PV String1 Current</t>
+        </is>
+      </c>
+      <c r="F116" s="3" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="G116" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H116" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I116" s="3" t="inlineStr"/>
+      <c r="J116" s="3" t="inlineStr"/>
+      <c r="K116" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L116" s="3" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="3" t="n">
+        <v>115</v>
+      </c>
+      <c r="B117" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C117" s="3" t="inlineStr">
+        <is>
+          <t>0x035C</t>
+        </is>
+      </c>
+      <c r="D117" s="3" t="n">
+        <v>860</v>
+      </c>
+      <c r="E117" s="3" t="inlineStr">
+        <is>
+          <t>Istr2/PV String2 Current</t>
+        </is>
+      </c>
+      <c r="F117" s="3" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="G117" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H117" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I117" s="3" t="inlineStr"/>
+      <c r="J117" s="3" t="inlineStr"/>
+      <c r="K117" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L117" s="3" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="3" t="n">
+        <v>116</v>
+      </c>
+      <c r="B118" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C118" s="3" t="inlineStr">
+        <is>
+          <t>0x035D</t>
+        </is>
+      </c>
+      <c r="D118" s="3" t="n">
+        <v>861</v>
+      </c>
+      <c r="E118" s="3" t="inlineStr">
+        <is>
+          <t>Istr3/PV String3 Current</t>
+        </is>
+      </c>
+      <c r="F118" s="3" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="G118" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H118" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I118" s="3" t="inlineStr"/>
+      <c r="J118" s="3" t="inlineStr"/>
+      <c r="K118" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L118" s="3" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="3" t="n">
+        <v>117</v>
+      </c>
+      <c r="B119" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C119" s="3" t="inlineStr">
+        <is>
+          <t>0x035E</t>
+        </is>
+      </c>
+      <c r="D119" s="3" t="n">
+        <v>862</v>
+      </c>
+      <c r="E119" s="3" t="inlineStr">
+        <is>
+          <t>Istr4/PV String4 Current</t>
+        </is>
+      </c>
+      <c r="F119" s="3" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="G119" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H119" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I119" s="3" t="inlineStr"/>
+      <c r="J119" s="3" t="inlineStr"/>
+      <c r="K119" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L119" s="3" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="3" t="n">
+        <v>118</v>
+      </c>
+      <c r="B120" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C120" s="3" t="inlineStr">
+        <is>
+          <t>0x035F</t>
+        </is>
+      </c>
+      <c r="D120" s="3" t="n">
+        <v>863</v>
+      </c>
+      <c r="E120" s="3" t="inlineStr">
+        <is>
+          <t>Istr5/PV String5 Current</t>
+        </is>
+      </c>
+      <c r="F120" s="3" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="G120" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H120" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I120" s="3" t="inlineStr"/>
+      <c r="J120" s="3" t="inlineStr"/>
+      <c r="K120" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L120" s="3" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="3" t="n">
+        <v>119</v>
+      </c>
+      <c r="B121" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C121" s="3" t="inlineStr">
+        <is>
+          <t>0x0360</t>
+        </is>
+      </c>
+      <c r="D121" s="3" t="n">
+        <v>864</v>
+      </c>
+      <c r="E121" s="3" t="inlineStr">
+        <is>
+          <t>Istr6/PV String6 Current</t>
+        </is>
+      </c>
+      <c r="F121" s="3" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="G121" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H121" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I121" s="3" t="inlineStr"/>
+      <c r="J121" s="3" t="inlineStr"/>
+      <c r="K121" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L121" s="3" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="B122" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C122" s="3" t="inlineStr">
+        <is>
+          <t>0x0361</t>
+        </is>
+      </c>
+      <c r="D122" s="3" t="n">
+        <v>865</v>
+      </c>
+      <c r="E122" s="3" t="inlineStr">
+        <is>
+          <t>Istr7/PV String7 Current</t>
+        </is>
+      </c>
+      <c r="F122" s="3" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="G122" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H122" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I122" s="3" t="inlineStr"/>
+      <c r="J122" s="3" t="inlineStr"/>
+      <c r="K122" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L122" s="3" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="3" t="n">
+        <v>121</v>
+      </c>
+      <c r="B123" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C123" s="3" t="inlineStr">
+        <is>
+          <t>0x0362</t>
+        </is>
+      </c>
+      <c r="D123" s="3" t="n">
+        <v>866</v>
+      </c>
+      <c r="E123" s="3" t="inlineStr">
+        <is>
+          <t>Istr8/PV String8 Current</t>
+        </is>
+      </c>
+      <c r="F123" s="3" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="G123" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H123" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I123" s="3" t="inlineStr"/>
+      <c r="J123" s="3" t="inlineStr"/>
+      <c r="K123" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L123" s="3" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="3" t="n">
+        <v>122</v>
+      </c>
+      <c r="B124" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C124" s="3" t="inlineStr">
+        <is>
+          <t>0x0363</t>
+        </is>
+      </c>
+      <c r="D124" s="3" t="n">
+        <v>867</v>
+      </c>
+      <c r="E124" s="3" t="inlineStr">
+        <is>
+          <t>Istr9/PV String9 Current</t>
+        </is>
+      </c>
+      <c r="F124" s="3" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="G124" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H124" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I124" s="3" t="inlineStr"/>
+      <c r="J124" s="3" t="inlineStr"/>
+      <c r="K124" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L124" s="3" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="3" t="n">
+        <v>123</v>
+      </c>
+      <c r="B125" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C125" s="3" t="inlineStr">
+        <is>
+          <t>0x0364</t>
+        </is>
+      </c>
+      <c r="D125" s="3" t="n">
+        <v>868</v>
+      </c>
+      <c r="E125" s="3" t="inlineStr">
+        <is>
+          <t>Istr10/PV String10 Current</t>
+        </is>
+      </c>
+      <c r="F125" s="3" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="G125" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H125" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I125" s="3" t="inlineStr"/>
+      <c r="J125" s="3" t="inlineStr"/>
+      <c r="K125" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L125" s="3" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="3" t="n">
+        <v>124</v>
+      </c>
+      <c r="B126" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C126" s="3" t="inlineStr">
+        <is>
+          <t>0x0365</t>
+        </is>
+      </c>
+      <c r="D126" s="3" t="n">
+        <v>869</v>
+      </c>
+      <c r="E126" s="3" t="inlineStr">
+        <is>
+          <t>Istr11/PV String11 Current</t>
+        </is>
+      </c>
+      <c r="F126" s="3" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="G126" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H126" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I126" s="3" t="inlineStr"/>
+      <c r="J126" s="3" t="inlineStr"/>
+      <c r="K126" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L126" s="3" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="3" t="n">
+        <v>125</v>
+      </c>
+      <c r="B127" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C127" s="3" t="inlineStr">
+        <is>
+          <t>0x0366</t>
+        </is>
+      </c>
+      <c r="D127" s="3" t="n">
+        <v>870</v>
+      </c>
+      <c r="E127" s="3" t="inlineStr">
+        <is>
+          <t>Istr12/PV String12 Current</t>
+        </is>
+      </c>
+      <c r="F127" s="3" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="G127" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H127" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I127" s="3" t="inlineStr"/>
+      <c r="J127" s="3" t="inlineStr"/>
+      <c r="K127" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L127" s="3" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="3" t="n">
+        <v>126</v>
+      </c>
+      <c r="B128" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C128" s="3" t="inlineStr">
+        <is>
+          <t>0x0367</t>
+        </is>
+      </c>
+      <c r="D128" s="3" t="n">
+        <v>871</v>
+      </c>
+      <c r="E128" s="3" t="inlineStr">
+        <is>
+          <t>Istr13/PV String13 Current</t>
+        </is>
+      </c>
+      <c r="F128" s="3" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="G128" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H128" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I128" s="3" t="inlineStr"/>
+      <c r="J128" s="3" t="inlineStr"/>
+      <c r="K128" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L128" s="3" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="3" t="n">
+        <v>127</v>
+      </c>
+      <c r="B129" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C129" s="3" t="inlineStr">
+        <is>
+          <t>0x0368</t>
+        </is>
+      </c>
+      <c r="D129" s="3" t="n">
+        <v>872</v>
+      </c>
+      <c r="E129" s="3" t="inlineStr">
+        <is>
+          <t>Istr14/PV String14 Current</t>
+        </is>
+      </c>
+      <c r="F129" s="3" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="G129" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H129" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I129" s="3" t="inlineStr"/>
+      <c r="J129" s="3" t="inlineStr"/>
+      <c r="K129" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L129" s="3" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="B130" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C130" s="3" t="inlineStr">
+        <is>
+          <t>0x0369</t>
+        </is>
+      </c>
+      <c r="D130" s="3" t="n">
+        <v>873</v>
+      </c>
+      <c r="E130" s="3" t="inlineStr">
+        <is>
+          <t>Istr15/PV String15 Current</t>
+        </is>
+      </c>
+      <c r="F130" s="3" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="G130" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H130" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I130" s="3" t="inlineStr"/>
+      <c r="J130" s="3" t="inlineStr"/>
+      <c r="K130" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L130" s="3" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="3" t="n">
+        <v>129</v>
+      </c>
+      <c r="B131" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C131" s="3" t="inlineStr">
+        <is>
+          <t>0x036A</t>
+        </is>
+      </c>
+      <c r="D131" s="3" t="n">
+        <v>874</v>
+      </c>
+      <c r="E131" s="3" t="inlineStr">
+        <is>
+          <t>Istr16/PV String16 Current</t>
+        </is>
+      </c>
+      <c r="F131" s="3" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="G131" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H131" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I131" s="3" t="inlineStr"/>
+      <c r="J131" s="3" t="inlineStr"/>
+      <c r="K131" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L131" s="3" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="3" t="n">
+        <v>130</v>
+      </c>
+      <c r="B132" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C132" s="3" t="inlineStr">
+        <is>
+          <t>0x036B</t>
+        </is>
+      </c>
+      <c r="D132" s="3" t="n">
+        <v>875</v>
+      </c>
+      <c r="E132" s="3" t="inlineStr">
+        <is>
+          <t>Istr17/PV String17 Current</t>
+        </is>
+      </c>
+      <c r="F132" s="3" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="G132" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H132" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I132" s="3" t="inlineStr"/>
+      <c r="J132" s="3" t="inlineStr"/>
+      <c r="K132" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L132" s="3" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="3" t="n">
+        <v>131</v>
+      </c>
+      <c r="B133" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C133" s="3" t="inlineStr">
+        <is>
+          <t>0x036C</t>
+        </is>
+      </c>
+      <c r="D133" s="3" t="n">
+        <v>876</v>
+      </c>
+      <c r="E133" s="3" t="inlineStr">
+        <is>
+          <t>Istr18/PV String18 Current</t>
+        </is>
+      </c>
+      <c r="F133" s="3" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="G133" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H133" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I133" s="3" t="inlineStr"/>
+      <c r="J133" s="3" t="inlineStr"/>
+      <c r="K133" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L133" s="3" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="3" t="n">
+        <v>132</v>
+      </c>
+      <c r="B134" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C134" s="3" t="inlineStr">
+        <is>
+          <t>0x036D</t>
+        </is>
+      </c>
+      <c r="D134" s="3" t="n">
+        <v>877</v>
+      </c>
+      <c r="E134" s="3" t="inlineStr">
+        <is>
+          <t>Istr19/PV String19 Current</t>
+        </is>
+      </c>
+      <c r="F134" s="3" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="G134" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H134" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I134" s="3" t="inlineStr"/>
+      <c r="J134" s="3" t="inlineStr"/>
+      <c r="K134" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L134" s="3" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="B135" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C135" s="3" t="inlineStr">
+        <is>
+          <t>0x036E</t>
+        </is>
+      </c>
+      <c r="D135" s="3" t="n">
+        <v>878</v>
+      </c>
+      <c r="E135" s="3" t="inlineStr">
+        <is>
+          <t>Istr20/PV String20 Current</t>
+        </is>
+      </c>
+      <c r="F135" s="3" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="G135" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H135" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I135" s="3" t="inlineStr"/>
+      <c r="J135" s="3" t="inlineStr"/>
+      <c r="K135" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L135" s="3" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="B136" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C136" s="3" t="inlineStr">
+        <is>
+          <t>0x036F</t>
+        </is>
+      </c>
+      <c r="D136" s="3" t="n">
+        <v>879</v>
+      </c>
+      <c r="E136" s="3" t="inlineStr">
+        <is>
+          <t>PID&amp;SPD Status</t>
+        </is>
+      </c>
+      <c r="F136" s="3" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="G136" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H136" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I136" s="3" t="inlineStr"/>
+      <c r="J136" s="3" t="inlineStr"/>
+      <c r="K136" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L136" s="3" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="3" t="n">
+        <v>135</v>
+      </c>
+      <c r="B137" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C137" s="3" t="inlineStr">
+        <is>
+          <t>0x0370</t>
+        </is>
+      </c>
+      <c r="D137" s="3" t="n">
+        <v>880</v>
+      </c>
+      <c r="E137" s="3" t="inlineStr">
+        <is>
+          <t>Output control state</t>
+        </is>
+      </c>
+      <c r="F137" s="3" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="G137" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H137" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I137" s="3" t="inlineStr"/>
+      <c r="J137" s="3" t="inlineStr"/>
+      <c r="K137" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L137" s="3" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="3" t="n">
+        <v>136</v>
+      </c>
+      <c r="B138" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C138" s="3" t="inlineStr">
+        <is>
+          <t>0x0376</t>
+        </is>
+      </c>
+      <c r="D138" s="3" t="n">
+        <v>886</v>
+      </c>
+      <c r="E138" s="3" t="inlineStr">
+        <is>
+          <t>Power Factor</t>
+        </is>
+      </c>
+      <c r="F138" s="3" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="G138" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H138" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I138" s="3" t="inlineStr"/>
+      <c r="J138" s="3" t="inlineStr"/>
+      <c r="K138" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L138" s="3" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="3" t="n">
+        <v>137</v>
+      </c>
+      <c r="B139" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C139" s="3" t="inlineStr">
+        <is>
+          <t>0x03E8</t>
+        </is>
+      </c>
+      <c r="D139" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E139" s="3" t="inlineStr">
+        <is>
+          <t>NA Power Factor</t>
+        </is>
+      </c>
+      <c r="F139" s="3" t="inlineStr"/>
+      <c r="G139" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H139" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I139" s="3" t="inlineStr"/>
+      <c r="J139" s="3" t="inlineStr"/>
+      <c r="K139" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L139" s="3" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="3" t="n">
+        <v>138</v>
+      </c>
+      <c r="B140" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C140" s="3" t="inlineStr">
+        <is>
+          <t>0x037D</t>
+        </is>
+      </c>
+      <c r="D140" s="3" t="n">
+        <v>893</v>
+      </c>
+      <c r="E140" s="3" t="inlineStr">
+        <is>
+          <t>High Byte of AC reactive power</t>
+        </is>
+      </c>
+      <c r="F140" s="3" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="G140" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H140" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I140" s="3" t="inlineStr"/>
+      <c r="J140" s="3" t="inlineStr"/>
+      <c r="K140" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L140" s="3" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="3" t="n">
+        <v>139</v>
+      </c>
+      <c r="B141" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C141" s="3" t="inlineStr">
+        <is>
+          <t>0x03E8</t>
+        </is>
+      </c>
+      <c r="D141" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E141" s="3" t="inlineStr">
+        <is>
+          <t>kVar AC reactive power high byte</t>
+        </is>
+      </c>
+      <c r="F141" s="3" t="inlineStr"/>
+      <c r="G141" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H141" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I141" s="3" t="inlineStr"/>
+      <c r="J141" s="3" t="inlineStr"/>
+      <c r="K141" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L141" s="3" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="3" t="n">
+        <v>140</v>
+      </c>
+      <c r="B142" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C142" s="3" t="inlineStr">
+        <is>
+          <t>0x037E</t>
+        </is>
+      </c>
+      <c r="D142" s="3" t="n">
+        <v>894</v>
+      </c>
+      <c r="E142" s="3" t="inlineStr">
+        <is>
+          <t>Low Byte of AC reactive power</t>
+        </is>
+      </c>
+      <c r="F142" s="3" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="G142" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H142" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I142" s="3" t="inlineStr"/>
+      <c r="J142" s="3" t="inlineStr"/>
+      <c r="K142" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L142" s="3" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="3" t="n">
+        <v>141</v>
+      </c>
+      <c r="B143" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C143" s="3" t="inlineStr">
+        <is>
+          <t>0x03E8</t>
+        </is>
+      </c>
+      <c r="D143" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E143" s="3" t="inlineStr">
+        <is>
+          <t>kVar AC reactive power low byte</t>
+        </is>
+      </c>
+      <c r="F143" s="3" t="inlineStr"/>
+      <c r="G143" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H143" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I143" s="3" t="inlineStr"/>
+      <c r="J143" s="3" t="inlineStr"/>
+      <c r="K143" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L143" s="3" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="3" t="n">
+        <v>142</v>
+      </c>
+      <c r="B144" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C144" s="3" t="inlineStr">
+        <is>
+          <t>0x037F</t>
+        </is>
+      </c>
+      <c r="D144" s="3" t="n">
+        <v>895</v>
+      </c>
+      <c r="E144" s="3" t="inlineStr">
+        <is>
+          <t>ISO detection value</t>
+        </is>
+      </c>
+      <c r="F144" s="3" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="G144" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H144" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I144" s="3" t="inlineStr"/>
+      <c r="J144" s="3" t="inlineStr"/>
+      <c r="K144" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L144" s="3" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="3" t="n">
+        <v>143</v>
+      </c>
+      <c r="B145" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C145" s="3" t="inlineStr">
+        <is>
+          <t>0x0380</t>
+        </is>
+      </c>
+      <c r="D145" s="3" t="n">
+        <v>896</v>
+      </c>
+      <c r="E145" s="3" t="inlineStr">
+        <is>
+          <t>Leak current Value</t>
+        </is>
+      </c>
+      <c r="F145" s="3" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="G145" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H145" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I145" s="3" t="inlineStr"/>
+      <c r="J145" s="3" t="inlineStr"/>
+      <c r="K145" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L145" s="3" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="3" t="n">
+        <v>144</v>
+      </c>
+      <c r="B146" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C146" s="3" t="inlineStr">
+        <is>
+          <t>0x03E8</t>
+        </is>
+      </c>
+      <c r="D146" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E146" s="3" t="inlineStr">
+        <is>
+          <t>Current R phase size</t>
+        </is>
+      </c>
+      <c r="F146" s="3" t="inlineStr">
+        <is>
+          <t>U32</t>
+        </is>
+      </c>
+      <c r="G146" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H146" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I146" s="3" t="inlineStr"/>
+      <c r="J146" s="3" t="inlineStr"/>
+      <c r="K146" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L146" s="3" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="3" t="n">
+        <v>145</v>
+      </c>
+      <c r="B147" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C147" s="3" t="inlineStr">
+        <is>
+          <t>0x03EA</t>
+        </is>
+      </c>
+      <c r="D147" s="3" t="n">
+        <v>1002</v>
+      </c>
+      <c r="E147" s="3" t="inlineStr">
+        <is>
+          <t>Current S phase size</t>
+        </is>
+      </c>
+      <c r="F147" s="3" t="inlineStr">
+        <is>
+          <t>U32</t>
+        </is>
+      </c>
+      <c r="G147" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H147" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I147" s="3" t="inlineStr"/>
+      <c r="J147" s="3" t="inlineStr"/>
+      <c r="K147" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L147" s="3" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="3" t="n">
+        <v>146</v>
+      </c>
+      <c r="B148" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C148" s="3" t="inlineStr">
+        <is>
+          <t>0x03EC</t>
+        </is>
+      </c>
+      <c r="D148" s="3" t="n">
+        <v>1004</v>
+      </c>
+      <c r="E148" s="3" t="inlineStr">
+        <is>
+          <t>Current T phase size</t>
+        </is>
+      </c>
+      <c r="F148" s="3" t="inlineStr">
+        <is>
+          <t>U32</t>
+        </is>
+      </c>
+      <c r="G148" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H148" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I148" s="3" t="inlineStr"/>
+      <c r="J148" s="3" t="inlineStr"/>
+      <c r="K148" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L148" s="3" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="3" t="n">
+        <v>147</v>
+      </c>
+      <c r="B149" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C149" s="3" t="inlineStr">
+        <is>
+          <t>0x03EE</t>
+        </is>
+      </c>
+      <c r="D149" s="3" t="n">
+        <v>1006</v>
+      </c>
+      <c r="E149" s="3" t="inlineStr">
+        <is>
+          <t>Current R phase size</t>
+        </is>
+      </c>
+      <c r="F149" s="3" t="inlineStr">
+        <is>
+          <t>U32</t>
+        </is>
+      </c>
+      <c r="G149" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H149" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I149" s="3" t="inlineStr"/>
+      <c r="J149" s="3" t="inlineStr"/>
+      <c r="K149" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L149" s="3" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="3" t="n">
+        <v>148</v>
+      </c>
+      <c r="B150" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C150" s="3" t="inlineStr">
+        <is>
+          <t>0x03F0</t>
+        </is>
+      </c>
+      <c r="D150" s="3" t="n">
+        <v>1008</v>
+      </c>
+      <c r="E150" s="3" t="inlineStr">
+        <is>
+          <t>Current S phase size</t>
+        </is>
+      </c>
+      <c r="F150" s="3" t="inlineStr">
+        <is>
+          <t>U32</t>
+        </is>
+      </c>
+      <c r="G150" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H150" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I150" s="3" t="inlineStr"/>
+      <c r="J150" s="3" t="inlineStr"/>
+      <c r="K150" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L150" s="3" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="3" t="n">
+        <v>149</v>
+      </c>
+      <c r="B151" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C151" s="3" t="inlineStr">
+        <is>
+          <t>0x03F2</t>
+        </is>
+      </c>
+      <c r="D151" s="3" t="n">
+        <v>1010</v>
+      </c>
+      <c r="E151" s="3" t="inlineStr">
+        <is>
+          <t>Current T phase size</t>
+        </is>
+      </c>
+      <c r="F151" s="3" t="inlineStr">
+        <is>
+          <t>U32</t>
+        </is>
+      </c>
+      <c r="G151" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H151" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I151" s="3" t="inlineStr"/>
+      <c r="J151" s="3" t="inlineStr"/>
+      <c r="K151" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L151" s="3" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="3" t="n">
+        <v>150</v>
+      </c>
+      <c r="B152" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C152" s="3" t="inlineStr">
+        <is>
+          <t>0x03F4</t>
+        </is>
+      </c>
+      <c r="D152" s="3" t="n">
+        <v>1012</v>
+      </c>
+      <c r="E152" s="3" t="inlineStr">
+        <is>
+          <t>3 phase effective power</t>
+        </is>
+      </c>
+      <c r="F152" s="3" t="inlineStr">
+        <is>
+          <t>U32</t>
+        </is>
+      </c>
+      <c r="G152" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H152" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I152" s="3" t="inlineStr"/>
+      <c r="J152" s="3" t="inlineStr"/>
+      <c r="K152" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L152" s="3" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="3" t="n">
+        <v>151</v>
+      </c>
+      <c r="B153" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C153" s="3" t="inlineStr">
+        <is>
+          <t>0x03F6</t>
+        </is>
+      </c>
+      <c r="D153" s="3" t="n">
+        <v>1014</v>
+      </c>
+      <c r="E153" s="3" t="inlineStr">
+        <is>
+          <t>3 phase ineffective power</t>
+        </is>
+      </c>
+      <c r="F153" s="3" t="inlineStr">
+        <is>
+          <t>U32</t>
+        </is>
+      </c>
+      <c r="G153" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H153" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I153" s="3" t="inlineStr"/>
+      <c r="J153" s="3" t="inlineStr"/>
+      <c r="K153" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L153" s="3" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="3" t="n">
+        <v>152</v>
+      </c>
+      <c r="B154" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C154" s="3" t="inlineStr">
+        <is>
+          <t>0x03F8</t>
+        </is>
+      </c>
+      <c r="D154" s="3" t="n">
+        <v>1016</v>
+      </c>
+      <c r="E154" s="3" t="inlineStr">
+        <is>
+          <t>3 Phase force rate</t>
+        </is>
+      </c>
+      <c r="F154" s="3" t="inlineStr"/>
+      <c r="G154" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H154" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I154" s="3" t="inlineStr"/>
+      <c r="J154" s="3" t="inlineStr"/>
+      <c r="K154" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L154" s="3" t="inlineStr">
+        <is>
+          <t>I32</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="3" t="n">
+        <v>153</v>
+      </c>
+      <c r="B155" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C155" s="3" t="inlineStr">
+        <is>
+          <t>0x03E8</t>
+        </is>
+      </c>
+      <c r="D155" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E155" s="3" t="inlineStr">
+        <is>
+          <t>0.001 (+ PF): 800~1000 (- PF):-800~- 1000,-1000 Handled as PF=1</t>
+        </is>
+      </c>
+      <c r="F155" s="3" t="inlineStr"/>
+      <c r="G155" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H155" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I155" s="3" t="inlineStr"/>
+      <c r="J155" s="3" t="inlineStr"/>
+      <c r="K155" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L155" s="3" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="3" t="n">
+        <v>154</v>
+      </c>
+      <c r="B156" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C156" s="3" t="inlineStr">
+        <is>
+          <t>0x03FA</t>
+        </is>
+      </c>
+      <c r="D156" s="3" t="n">
+        <v>1018</v>
+      </c>
+      <c r="E156" s="3" t="inlineStr">
+        <is>
+          <t>Frequency</t>
+        </is>
+      </c>
+      <c r="F156" s="3" t="inlineStr">
+        <is>
+          <t>U32</t>
+        </is>
+      </c>
+      <c r="G156" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H156" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I156" s="3" t="inlineStr"/>
+      <c r="J156" s="3" t="inlineStr"/>
+      <c r="K156" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L156" s="3" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="3" t="n">
+        <v>155</v>
+      </c>
+      <c r="B157" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C157" s="3" t="inlineStr">
+        <is>
+          <t>0x03FC</t>
+        </is>
+      </c>
+      <c r="D157" s="3" t="n">
+        <v>1020</v>
+      </c>
+      <c r="E157" s="3" t="inlineStr">
+        <is>
+          <t>Status Flag1</t>
+        </is>
+      </c>
+      <c r="F157" s="3" t="inlineStr">
+        <is>
+          <t>U32</t>
+        </is>
+      </c>
+      <c r="G157" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H157" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I157" s="3" t="inlineStr"/>
+      <c r="J157" s="3" t="inlineStr"/>
+      <c r="K157" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L157" s="3" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="3" t="n">
+        <v>156</v>
+      </c>
+      <c r="B158" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C158" s="3" t="inlineStr">
+        <is>
+          <t>0x07D0</t>
+        </is>
+      </c>
+      <c r="D158" s="3" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E158" s="3" t="inlineStr">
+        <is>
+          <t>PF WR</t>
+        </is>
+      </c>
+      <c r="F158" s="3" t="inlineStr">
+        <is>
+          <t>S16</t>
+        </is>
+      </c>
+      <c r="G158" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H158" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I158" s="3" t="inlineStr"/>
+      <c r="J158" s="3" t="inlineStr"/>
+      <c r="K158" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L158" s="3" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="3" t="n">
+        <v>157</v>
+      </c>
+      <c r="B159" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C159" s="3" t="inlineStr">
+        <is>
+          <t>0x03E8</t>
+        </is>
+      </c>
+      <c r="D159" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E159" s="3" t="inlineStr">
+        <is>
+          <t>0.001 (+ PF): 800~1000 (- PF):-800~-990</t>
+        </is>
+      </c>
+      <c r="F159" s="3" t="inlineStr"/>
+      <c r="G159" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H159" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I159" s="3" t="inlineStr"/>
+      <c r="J159" s="3" t="inlineStr"/>
+      <c r="K159" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L159" s="3" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="3" t="n">
+        <v>158</v>
+      </c>
+      <c r="B160" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C160" s="3" t="inlineStr">
+        <is>
+          <t>0x07D1</t>
+        </is>
+      </c>
+      <c r="D160" s="3" t="n">
+        <v>2001</v>
+      </c>
+      <c r="E160" s="3" t="inlineStr">
+        <is>
+          <t>Work and Mode WR</t>
+        </is>
+      </c>
+      <c r="F160" s="3" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="G160" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H160" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I160" s="3" t="inlineStr"/>
+      <c r="J160" s="3" t="inlineStr"/>
+      <c r="K160" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L160" s="3" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="3" t="n">
+        <v>159</v>
+      </c>
+      <c r="B161" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C161" s="3" t="inlineStr">
+        <is>
+          <t>0x07D2</t>
+        </is>
+      </c>
+      <c r="D161" s="3" t="n">
+        <v>2002</v>
+      </c>
+      <c r="E161" s="3" t="inlineStr">
+        <is>
+          <t>Constant Reactive Power WR</t>
+        </is>
+      </c>
+      <c r="F161" s="3" t="inlineStr">
+        <is>
+          <t>S16</t>
+        </is>
+      </c>
+      <c r="G161" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H161" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I161" s="3" t="inlineStr"/>
+      <c r="J161" s="3" t="inlineStr"/>
+      <c r="K161" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L161" s="3" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="3" t="n">
+        <v>160</v>
+      </c>
+      <c r="B162" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C162" s="3" t="inlineStr">
+        <is>
+          <t>0x07D3</t>
+        </is>
+      </c>
+      <c r="D162" s="3" t="n">
+        <v>2003</v>
+      </c>
+      <c r="E162" s="3" t="inlineStr">
+        <is>
+          <t>Constant Active Power WR</t>
+        </is>
+      </c>
+      <c r="F162" s="3" t="inlineStr">
+        <is>
+          <t>U16</t>
+        </is>
+      </c>
+      <c r="G162" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H162" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I162" s="3" t="inlineStr"/>
+      <c r="J162" s="3" t="inlineStr"/>
+      <c r="K162" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L162" s="3" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="3" t="n">
+        <v>161</v>
+      </c>
+      <c r="B163" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C163" s="3" t="inlineStr">
+        <is>
+          <t>0x0002</t>
+        </is>
+      </c>
+      <c r="D163" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E163" s="3" t="inlineStr">
+        <is>
+          <t>Utility Loss 1. Grid power fails.|2. AC connection is not good.|3. AC breaker fails 4. Grid is not connected. Bit8</t>
+        </is>
+      </c>
+      <c r="F163" s="3" t="inlineStr"/>
+      <c r="G163" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H163" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I163" s="3" t="inlineStr"/>
+      <c r="J163" s="3" t="inlineStr"/>
+      <c r="K163" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L163" s="3" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="3" t="n">
+        <v>162</v>
+      </c>
+      <c r="B164" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C164" s="3" t="inlineStr">
+        <is>
+          <t>0x0001</t>
+        </is>
+      </c>
+      <c r="D164" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E164" s="3" t="inlineStr">
+        <is>
+          <t>AC HCT Fail 1. An occasional situation, caused by external factors like external magnetic field etc.|2. Control board has a problem. Bit7</t>
+        </is>
+      </c>
+      <c r="F164" s="3" t="inlineStr"/>
+      <c r="G164" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H164" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I164" s="3" t="inlineStr"/>
+      <c r="J164" s="3" t="inlineStr"/>
+      <c r="K164" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L164" s="3" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="3" t="n">
+        <v>163</v>
+      </c>
+      <c r="B165" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C165" s="3" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="D165" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E165" s="3" t="inlineStr">
+        <is>
+          <t>Relay Fail 1. An occasional situation, caused by external factors like external magnetic field etc.|2. Control board has a problem. Bit6</t>
+        </is>
+      </c>
+      <c r="F165" s="3" t="inlineStr"/>
+      <c r="G165" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H165" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I165" s="3" t="inlineStr"/>
+      <c r="J165" s="3" t="inlineStr"/>
+      <c r="K165" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L165" s="3" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="3" t="n">
+        <v>164</v>
+      </c>
+      <c r="B166" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C166" s="3" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="D166" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E166" s="3" t="inlineStr">
+        <is>
+          <t>GFCI Fail 1. An occasional situation, caused by external factors like external magnetic field etc.|2. Control board has a problem. Bit5</t>
+        </is>
+      </c>
+      <c r="F166" s="3" t="inlineStr"/>
+      <c r="G166" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H166" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I166" s="3" t="inlineStr"/>
+      <c r="J166" s="3" t="inlineStr"/>
+      <c r="K166" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L166" s="3" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="3" t="n">
+        <v>165</v>
+      </c>
+      <c r="B167" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C167" s="3" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="D167" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E167" s="3" t="inlineStr">
+        <is>
+          <t>00000020 Please contact after sales. Bit4</t>
+        </is>
+      </c>
+      <c r="F167" s="3" t="inlineStr"/>
+      <c r="G167" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H167" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I167" s="3" t="inlineStr"/>
+      <c r="J167" s="3" t="inlineStr"/>
+      <c r="K167" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L167" s="3" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="3" t="n">
+        <v>166</v>
+      </c>
+      <c r="B168" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C168" s="3" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="D168" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E168" s="3" t="inlineStr">
+        <is>
+          <t>DC SPD Fail Inverter suffering from lighting strike Bit3</t>
+        </is>
+      </c>
+      <c r="F168" s="3" t="inlineStr"/>
+      <c r="G168" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H168" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I168" s="3" t="inlineStr"/>
+      <c r="J168" s="3" t="inlineStr"/>
+      <c r="K168" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L168" s="3" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="3" t="n">
+        <v>167</v>
+      </c>
+      <c r="B169" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C169" s="3" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="D169" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E169" s="3" t="inlineStr">
+        <is>
+          <t>DC Switch Fail The number of times of use of the DC trip switch exceeds the service life Bit2</t>
+        </is>
+      </c>
+      <c r="F169" s="3" t="inlineStr"/>
+      <c r="G169" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H169" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I169" s="3" t="inlineStr"/>
+      <c r="J169" s="3" t="inlineStr"/>
+      <c r="K169" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L169" s="3" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="3" t="n">
+        <v>168</v>
+      </c>
+      <c r="B170" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C170" s="3" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="D170" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E170" s="3" t="inlineStr">
+        <is>
+          <t>Ref 1.5V Fail 1. An occasional situation, caused by external factors like external magnetic field etc.|2. Control board has a problem. Bit1</t>
+        </is>
+      </c>
+      <c r="F170" s="3" t="inlineStr"/>
+      <c r="G170" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H170" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I170" s="3" t="inlineStr"/>
+      <c r="J170" s="3" t="inlineStr"/>
+      <c r="K170" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L170" s="3" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="3" t="n">
+        <v>169</v>
+      </c>
+      <c r="B171" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C171" s="3" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="D171" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E171" s="3" t="inlineStr">
+        <is>
+          <t>AC HCT Check Fail 1. Try to restart inverter, check if it still happens, if not, means it is just an occasional situation.|2. If restart cannot solve the problem, Please contact after sales. Bit0</t>
+        </is>
+      </c>
+      <c r="F171" s="3" t="inlineStr"/>
+      <c r="G171" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H171" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I171" s="3" t="inlineStr"/>
+      <c r="J171" s="3" t="inlineStr"/>
+      <c r="K171" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L171" s="3" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="3" t="n">
+        <v>170</v>
+      </c>
+      <c r="B172" s="3" t="inlineStr">
+        <is>
+          <t>Registers</t>
+        </is>
+      </c>
+      <c r="C172" s="3" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="D172" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E172" s="3" t="inlineStr">
+        <is>
+          <t>GFCI Check Fail 1. Try to restart inverter, check if it still happens, if not, means it is just an occasional situation.|2. If restart cannot solve the problem, Please contact after sales. Table 8-3 Bit No Status 1</t>
+        </is>
+      </c>
+      <c r="F172" s="3" t="inlineStr"/>
+      <c r="G172" s="3" t="inlineStr">
+        <is>
+          <t>FC03</t>
+        </is>
+      </c>
+      <c r="H172" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I172" s="3" t="inlineStr"/>
+      <c r="J172" s="3" t="inlineStr"/>
+      <c r="K172" s="3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="L172" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:L1"/>
+  <mergeCells count="1">
+    <mergeCell ref="A2:L2"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -579,36 +7984,36 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>Set : Separate, Reset : Contact 1</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Set : Separate, Reset : Contact 1</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr"/>
+      <c r="D2" s="3" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Separate operation</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>Separate operation</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr"/>
+      <c r="D3" s="3" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -666,1849 +8071,1849 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>792</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr"/>
-      <c r="C2" s="2" t="inlineStr"/>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr"/>
+      <c r="C2" s="3" t="inlineStr"/>
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>RSVD</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr"/>
+      <c r="E2" s="3" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>793</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr"/>
-      <c r="C3" s="2" t="inlineStr"/>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr"/>
+      <c r="C3" s="3" t="inlineStr"/>
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>Function Status</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr"/>
+      <c r="E3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>794</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr"/>
-      <c r="C4" s="2" t="inlineStr"/>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr"/>
+      <c r="C4" s="3" t="inlineStr"/>
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>RSVD</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr"/>
+      <c r="E4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>795</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr"/>
-      <c r="C5" s="2" t="inlineStr"/>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr"/>
+      <c r="C5" s="3" t="inlineStr"/>
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>RSVD</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr"/>
+      <c r="E5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>796</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr"/>
-      <c r="C6" s="2" t="inlineStr"/>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr"/>
+      <c r="C6" s="3" t="inlineStr"/>
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>BUS Voltage</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr"/>
+      <c r="E6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>797</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr"/>
-      <c r="C7" s="2" t="inlineStr"/>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr"/>
+      <c r="C7" s="3" t="inlineStr"/>
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>NBUS Voltage</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr"/>
+      <c r="E7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>798</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr"/>
-      <c r="C8" s="2" t="inlineStr"/>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr"/>
+      <c r="C8" s="3" t="inlineStr"/>
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>RSVD</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr"/>
+      <c r="E8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>799</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr"/>
-      <c r="C9" s="2" t="inlineStr"/>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr"/>
+      <c r="C9" s="3" t="inlineStr"/>
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>Safety Code</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr"/>
+      <c r="E9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>800</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr"/>
-      <c r="C10" s="2" t="inlineStr"/>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr"/>
+      <c r="C10" s="3" t="inlineStr"/>
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>Feed Power to</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr"/>
+      <c r="E10" s="3" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr"/>
-      <c r="C11" s="2" t="inlineStr"/>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr"/>
+      <c r="C11" s="3" t="inlineStr"/>
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>generation</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr"/>
+      <c r="E11" s="3" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>804</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr"/>
-      <c r="C12" s="2" t="inlineStr"/>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr"/>
+      <c r="C12" s="3" t="inlineStr"/>
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>Vpv5 /PV5 input</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr"/>
+      <c r="E12" s="3" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>805</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr"/>
-      <c r="C13" s="2" t="inlineStr"/>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr"/>
+      <c r="C13" s="3" t="inlineStr"/>
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>Ipv5 /PV5 input</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr"/>
+      <c r="E13" s="3" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>806</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr"/>
-      <c r="C14" s="2" t="inlineStr"/>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr"/>
+      <c r="C14" s="3" t="inlineStr"/>
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>Vpv6 /PV6 input</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr"/>
+      <c r="E14" s="3" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>807</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr"/>
-      <c r="C15" s="2" t="inlineStr"/>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr"/>
+      <c r="C15" s="3" t="inlineStr"/>
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>Ipv6 /PV6 input</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr"/>
+      <c r="E15" s="3" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>827</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr"/>
-      <c r="C16" s="2" t="inlineStr"/>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr"/>
+      <c r="C16" s="3" t="inlineStr"/>
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>Year :Month</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr"/>
+      <c r="E16" s="3" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>828</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr"/>
-      <c r="C17" s="2" t="inlineStr"/>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr"/>
+      <c r="C17" s="3" t="inlineStr"/>
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>Date :Hour</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr"/>
+      <c r="E17" s="3" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>829</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr"/>
-      <c r="C18" s="2" t="inlineStr"/>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr"/>
+      <c r="C18" s="3" t="inlineStr"/>
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t>Minute :Second</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr"/>
+      <c r="E18" s="3" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>830</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr"/>
-      <c r="C19" s="2" t="inlineStr"/>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr"/>
+      <c r="C19" s="3" t="inlineStr"/>
+      <c r="D19" s="3" t="inlineStr">
         <is>
           <t>Manufacture ID</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr"/>
+      <c r="E19" s="3" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>831</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr"/>
-      <c r="C20" s="2" t="inlineStr"/>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr"/>
+      <c r="C20" s="3" t="inlineStr"/>
+      <c r="D20" s="3" t="inlineStr">
         <is>
           <t>Wireless signal</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr"/>
+      <c r="E20" s="3" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>832</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr"/>
-      <c r="C21" s="2" t="inlineStr"/>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr"/>
+      <c r="C21" s="3" t="inlineStr"/>
+      <c r="D21" s="3" t="inlineStr">
         <is>
           <t>High Byte of PV</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr"/>
+      <c r="E21" s="3" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>833</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr"/>
-      <c r="C22" s="2" t="inlineStr"/>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr"/>
+      <c r="C22" s="3" t="inlineStr"/>
+      <c r="D22" s="3" t="inlineStr">
         <is>
           <t>Low Byte of PV</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr"/>
+      <c r="E22" s="3" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>850</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr"/>
-      <c r="C23" s="2" t="inlineStr"/>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr"/>
+      <c r="C23" s="3" t="inlineStr"/>
+      <c r="D23" s="3" t="inlineStr">
         <is>
           <t>High Byte of</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr"/>
+      <c r="E23" s="3" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t>851</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr"/>
-      <c r="C24" s="2" t="inlineStr"/>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="B24" s="3" t="inlineStr"/>
+      <c r="C24" s="3" t="inlineStr"/>
+      <c r="D24" s="3" t="inlineStr">
         <is>
           <t>Low Byte of</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr"/>
+      <c r="E24" s="3" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t>852</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr"/>
-      <c r="C25" s="2" t="inlineStr"/>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="B25" s="3" t="inlineStr"/>
+      <c r="C25" s="3" t="inlineStr"/>
+      <c r="D25" s="3" t="inlineStr">
         <is>
           <t>Firmware</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr"/>
+      <c r="E25" s="3" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>853</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr"/>
-      <c r="C26" s="2" t="inlineStr"/>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="B26" s="3" t="inlineStr"/>
+      <c r="C26" s="3" t="inlineStr"/>
+      <c r="D26" s="3" t="inlineStr">
         <is>
           <t>GPRS Burn-in</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr"/>
+      <c r="E26" s="3" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>0x00</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr"/>
-      <c r="C27" s="2" t="inlineStr"/>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="B27" s="3" t="inlineStr"/>
+      <c r="C27" s="3" t="inlineStr"/>
+      <c r="D27" s="3" t="inlineStr">
         <is>
           <t>normal mode</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr"/>
+      <c r="E27" s="3" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="A28" s="3" t="inlineStr">
         <is>
           <t>854</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr"/>
-      <c r="C28" s="2" t="inlineStr"/>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="B28" s="3" t="inlineStr"/>
+      <c r="C28" s="3" t="inlineStr"/>
+      <c r="D28" s="3" t="inlineStr">
         <is>
           <t>Pac H /High Byte</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr"/>
+      <c r="E28" s="3" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="A29" s="3" t="inlineStr">
         <is>
           <t>855</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr"/>
-      <c r="C29" s="2" t="inlineStr"/>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="B29" s="3" t="inlineStr"/>
+      <c r="C29" s="3" t="inlineStr"/>
+      <c r="D29" s="3" t="inlineStr">
         <is>
           <t>Vpv3 /PV3 input</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr"/>
+      <c r="E29" s="3" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="A30" s="3" t="inlineStr">
         <is>
           <t>856</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr"/>
-      <c r="C30" s="2" t="inlineStr"/>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="B30" s="3" t="inlineStr"/>
+      <c r="C30" s="3" t="inlineStr"/>
+      <c r="D30" s="3" t="inlineStr">
         <is>
           <t>Vpv4 /PV4 input</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr"/>
+      <c r="E30" s="3" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+      <c r="A31" s="3" t="inlineStr">
         <is>
           <t>857</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr"/>
-      <c r="C31" s="2" t="inlineStr"/>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="B31" s="3" t="inlineStr"/>
+      <c r="C31" s="3" t="inlineStr"/>
+      <c r="D31" s="3" t="inlineStr">
         <is>
           <t>Ipv3 /PV3 input</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr"/>
+      <c r="E31" s="3" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+      <c r="A32" s="3" t="inlineStr">
         <is>
           <t>858</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr"/>
-      <c r="C32" s="2" t="inlineStr"/>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="B32" s="3" t="inlineStr"/>
+      <c r="C32" s="3" t="inlineStr"/>
+      <c r="D32" s="3" t="inlineStr">
         <is>
           <t>Ipv4 /PV4 input</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr"/>
+      <c r="E32" s="3" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+      <c r="A33" s="3" t="inlineStr">
         <is>
           <t>859</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr"/>
-      <c r="C33" s="2" t="inlineStr"/>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="B33" s="3" t="inlineStr"/>
+      <c r="C33" s="3" t="inlineStr"/>
+      <c r="D33" s="3" t="inlineStr">
         <is>
           <t>Istr1/PV String1</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr"/>
+      <c r="E33" s="3" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="A34" s="3" t="inlineStr">
         <is>
           <t>860</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr"/>
-      <c r="C34" s="2" t="inlineStr"/>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="B34" s="3" t="inlineStr"/>
+      <c r="C34" s="3" t="inlineStr"/>
+      <c r="D34" s="3" t="inlineStr">
         <is>
           <t>Istr2/PV String2</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr"/>
+      <c r="E34" s="3" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+      <c r="A35" s="3" t="inlineStr">
         <is>
           <t>861</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr"/>
-      <c r="C35" s="2" t="inlineStr"/>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="B35" s="3" t="inlineStr"/>
+      <c r="C35" s="3" t="inlineStr"/>
+      <c r="D35" s="3" t="inlineStr">
         <is>
           <t>Istr3/PV String3</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr"/>
+      <c r="E35" s="3" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+      <c r="A36" s="3" t="inlineStr">
         <is>
           <t>862</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr"/>
-      <c r="C36" s="2" t="inlineStr"/>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="B36" s="3" t="inlineStr"/>
+      <c r="C36" s="3" t="inlineStr"/>
+      <c r="D36" s="3" t="inlineStr">
         <is>
           <t>Istr4/PV String4</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr"/>
+      <c r="E36" s="3" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+      <c r="A37" s="3" t="inlineStr">
         <is>
           <t>863</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr"/>
-      <c r="C37" s="2" t="inlineStr"/>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="B37" s="3" t="inlineStr"/>
+      <c r="C37" s="3" t="inlineStr"/>
+      <c r="D37" s="3" t="inlineStr">
         <is>
           <t>Istr5/PV String5</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr"/>
+      <c r="E37" s="3" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+      <c r="A38" s="3" t="inlineStr">
         <is>
           <t>864</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr"/>
-      <c r="C38" s="2" t="inlineStr"/>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="B38" s="3" t="inlineStr"/>
+      <c r="C38" s="3" t="inlineStr"/>
+      <c r="D38" s="3" t="inlineStr">
         <is>
           <t>Istr6/PV String6</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr"/>
+      <c r="E38" s="3" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+      <c r="A39" s="3" t="inlineStr">
         <is>
           <t>865</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr"/>
-      <c r="C39" s="2" t="inlineStr"/>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="B39" s="3" t="inlineStr"/>
+      <c r="C39" s="3" t="inlineStr"/>
+      <c r="D39" s="3" t="inlineStr">
         <is>
           <t>Istr7/PV String7</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr"/>
+      <c r="E39" s="3" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+      <c r="A40" s="3" t="inlineStr">
         <is>
           <t>866</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr"/>
-      <c r="C40" s="2" t="inlineStr"/>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="B40" s="3" t="inlineStr"/>
+      <c r="C40" s="3" t="inlineStr"/>
+      <c r="D40" s="3" t="inlineStr">
         <is>
           <t>Istr8/PV String8</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr"/>
+      <c r="E40" s="3" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+      <c r="A41" s="3" t="inlineStr">
         <is>
           <t>867</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr"/>
-      <c r="C41" s="2" t="inlineStr"/>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="B41" s="3" t="inlineStr"/>
+      <c r="C41" s="3" t="inlineStr"/>
+      <c r="D41" s="3" t="inlineStr">
         <is>
           <t>Istr9/PV String9</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr"/>
+      <c r="E41" s="3" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+      <c r="A42" s="3" t="inlineStr">
         <is>
           <t>868</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr"/>
-      <c r="C42" s="2" t="inlineStr"/>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="B42" s="3" t="inlineStr"/>
+      <c r="C42" s="3" t="inlineStr"/>
+      <c r="D42" s="3" t="inlineStr">
         <is>
           <t>Istr10/PV</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr"/>
+      <c r="E42" s="3" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+      <c r="A43" s="3" t="inlineStr">
         <is>
           <t>869</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr"/>
-      <c r="C43" s="2" t="inlineStr"/>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="B43" s="3" t="inlineStr"/>
+      <c r="C43" s="3" t="inlineStr"/>
+      <c r="D43" s="3" t="inlineStr">
         <is>
           <t>Istr11/PV</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr"/>
+      <c r="E43" s="3" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+      <c r="A44" s="3" t="inlineStr">
         <is>
           <t>870</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr"/>
-      <c r="C44" s="2" t="inlineStr"/>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="B44" s="3" t="inlineStr"/>
+      <c r="C44" s="3" t="inlineStr"/>
+      <c r="D44" s="3" t="inlineStr">
         <is>
           <t>Istr12/PV</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr"/>
+      <c r="E44" s="3" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+      <c r="A45" s="3" t="inlineStr">
         <is>
           <t>871</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr"/>
-      <c r="C45" s="2" t="inlineStr"/>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="B45" s="3" t="inlineStr"/>
+      <c r="C45" s="3" t="inlineStr"/>
+      <c r="D45" s="3" t="inlineStr">
         <is>
           <t>Istr13/PV</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr"/>
+      <c r="E45" s="3" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+      <c r="A46" s="3" t="inlineStr">
         <is>
           <t>872</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr"/>
-      <c r="C46" s="2" t="inlineStr"/>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="B46" s="3" t="inlineStr"/>
+      <c r="C46" s="3" t="inlineStr"/>
+      <c r="D46" s="3" t="inlineStr">
         <is>
           <t>Istr14/PV</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr"/>
+      <c r="E46" s="3" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+      <c r="A47" s="3" t="inlineStr">
         <is>
           <t>873</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr"/>
-      <c r="C47" s="2" t="inlineStr"/>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="B47" s="3" t="inlineStr"/>
+      <c r="C47" s="3" t="inlineStr"/>
+      <c r="D47" s="3" t="inlineStr">
         <is>
           <t>Istr15/PV</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr"/>
+      <c r="E47" s="3" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+      <c r="A48" s="3" t="inlineStr">
         <is>
           <t>874</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr"/>
-      <c r="C48" s="2" t="inlineStr"/>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="B48" s="3" t="inlineStr"/>
+      <c r="C48" s="3" t="inlineStr"/>
+      <c r="D48" s="3" t="inlineStr">
         <is>
           <t>Istr16/PV</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr"/>
+      <c r="E48" s="3" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+      <c r="A49" s="3" t="inlineStr">
         <is>
           <t>875</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr"/>
-      <c r="C49" s="2" t="inlineStr"/>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="B49" s="3" t="inlineStr"/>
+      <c r="C49" s="3" t="inlineStr"/>
+      <c r="D49" s="3" t="inlineStr">
         <is>
           <t>Istr17/PV</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr"/>
+      <c r="E49" s="3" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+      <c r="A50" s="3" t="inlineStr">
         <is>
           <t>876</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr"/>
-      <c r="C50" s="2" t="inlineStr"/>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="B50" s="3" t="inlineStr"/>
+      <c r="C50" s="3" t="inlineStr"/>
+      <c r="D50" s="3" t="inlineStr">
         <is>
           <t>Istr18/PV</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr"/>
+      <c r="E50" s="3" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+      <c r="A51" s="3" t="inlineStr">
         <is>
           <t>877</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr"/>
-      <c r="C51" s="2" t="inlineStr"/>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="B51" s="3" t="inlineStr"/>
+      <c r="C51" s="3" t="inlineStr"/>
+      <c r="D51" s="3" t="inlineStr">
         <is>
           <t>Istr19/PV</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr"/>
+      <c r="E51" s="3" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+      <c r="A52" s="3" t="inlineStr">
         <is>
           <t>878</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr"/>
-      <c r="C52" s="2" t="inlineStr"/>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="B52" s="3" t="inlineStr"/>
+      <c r="C52" s="3" t="inlineStr"/>
+      <c r="D52" s="3" t="inlineStr">
         <is>
           <t>Istr20/PV</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr"/>
+      <c r="E52" s="3" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+      <c r="A53" s="3" t="inlineStr">
         <is>
           <t>879</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr"/>
-      <c r="C53" s="2" t="inlineStr"/>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="B53" s="3" t="inlineStr"/>
+      <c r="C53" s="3" t="inlineStr"/>
+      <c r="D53" s="3" t="inlineStr">
         <is>
           <t>PID&amp;SPD Status</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr"/>
+      <c r="E53" s="3" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+      <c r="A54" s="3" t="inlineStr">
         <is>
           <t>880</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr"/>
-      <c r="C54" s="2" t="inlineStr"/>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="B54" s="3" t="inlineStr"/>
+      <c r="C54" s="3" t="inlineStr"/>
+      <c r="D54" s="3" t="inlineStr">
         <is>
           <t>Output control</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr"/>
+      <c r="E54" s="3" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+      <c r="A55" s="3" t="inlineStr">
         <is>
           <t>886</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr"/>
-      <c r="C55" s="2" t="inlineStr"/>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="B55" s="3" t="inlineStr"/>
+      <c r="C55" s="3" t="inlineStr"/>
+      <c r="D55" s="3" t="inlineStr">
         <is>
           <t>Power Factor</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr"/>
+      <c r="E55" s="3" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+      <c r="A56" s="3" t="inlineStr">
         <is>
           <t>893</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr"/>
-      <c r="C56" s="2" t="inlineStr"/>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="B56" s="3" t="inlineStr"/>
+      <c r="C56" s="3" t="inlineStr"/>
+      <c r="D56" s="3" t="inlineStr">
         <is>
           <t>High Byte of AC</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr"/>
+      <c r="E56" s="3" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+      <c r="A57" s="3" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr"/>
-      <c r="C57" s="2" t="inlineStr"/>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="B57" s="3" t="inlineStr"/>
+      <c r="C57" s="3" t="inlineStr"/>
+      <c r="D57" s="3" t="inlineStr">
         <is>
           <t>kVar</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr"/>
+      <c r="E57" s="3" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+      <c r="A58" s="3" t="inlineStr">
         <is>
           <t>894</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr"/>
-      <c r="C58" s="2" t="inlineStr"/>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="B58" s="3" t="inlineStr"/>
+      <c r="C58" s="3" t="inlineStr"/>
+      <c r="D58" s="3" t="inlineStr">
         <is>
           <t>Low Byte of AC</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr"/>
+      <c r="E58" s="3" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+      <c r="A59" s="3" t="inlineStr">
         <is>
           <t>895</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr"/>
-      <c r="C59" s="2" t="inlineStr"/>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="B59" s="3" t="inlineStr"/>
+      <c r="C59" s="3" t="inlineStr"/>
+      <c r="D59" s="3" t="inlineStr">
         <is>
           <t>ISO detection</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr"/>
+      <c r="E59" s="3" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+      <c r="A60" s="3" t="inlineStr">
         <is>
           <t>896</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr"/>
-      <c r="C60" s="2" t="inlineStr"/>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="B60" s="3" t="inlineStr"/>
+      <c r="C60" s="3" t="inlineStr"/>
+      <c r="D60" s="3" t="inlineStr">
         <is>
           <t>Leak current</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr"/>
+      <c r="E60" s="3" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+      <c r="A61" s="3" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr"/>
-      <c r="C61" s="2" t="inlineStr"/>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="B61" s="3" t="inlineStr"/>
+      <c r="C61" s="3" t="inlineStr"/>
+      <c r="D61" s="3" t="inlineStr">
         <is>
           <t>Current R phase</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr"/>
+      <c r="E61" s="3" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+      <c r="A62" s="3" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr"/>
-      <c r="C62" s="2" t="inlineStr"/>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="B62" s="3" t="inlineStr"/>
+      <c r="C62" s="3" t="inlineStr"/>
+      <c r="D62" s="3" t="inlineStr">
         <is>
           <t>0.1A</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr"/>
+      <c r="E62" s="3" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+      <c r="A63" s="3" t="inlineStr">
         <is>
           <t>1002</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr"/>
-      <c r="C63" s="2" t="inlineStr"/>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="B63" s="3" t="inlineStr"/>
+      <c r="C63" s="3" t="inlineStr"/>
+      <c r="D63" s="3" t="inlineStr">
         <is>
           <t>Current S phase</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr"/>
+      <c r="E63" s="3" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+      <c r="A64" s="3" t="inlineStr">
         <is>
           <t>1004</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr"/>
-      <c r="C64" s="2" t="inlineStr"/>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="B64" s="3" t="inlineStr"/>
+      <c r="C64" s="3" t="inlineStr"/>
+      <c r="D64" s="3" t="inlineStr">
         <is>
           <t>Current T phase</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr"/>
+      <c r="E64" s="3" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+      <c r="A65" s="3" t="inlineStr">
         <is>
           <t>1006</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr"/>
-      <c r="C65" s="2" t="inlineStr"/>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="B65" s="3" t="inlineStr"/>
+      <c r="C65" s="3" t="inlineStr"/>
+      <c r="D65" s="3" t="inlineStr">
         <is>
           <t>Current R phase</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr"/>
+      <c r="E65" s="3" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+      <c r="A66" s="3" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr"/>
-      <c r="C66" s="2" t="inlineStr"/>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="B66" s="3" t="inlineStr"/>
+      <c r="C66" s="3" t="inlineStr"/>
+      <c r="D66" s="3" t="inlineStr">
         <is>
           <t>0.1V</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr"/>
+      <c r="E66" s="3" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+      <c r="A67" s="3" t="inlineStr">
         <is>
           <t>1008</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr"/>
-      <c r="C67" s="2" t="inlineStr"/>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="B67" s="3" t="inlineStr"/>
+      <c r="C67" s="3" t="inlineStr"/>
+      <c r="D67" s="3" t="inlineStr">
         <is>
           <t>Current S phase</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr"/>
+      <c r="E67" s="3" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+      <c r="A68" s="3" t="inlineStr">
         <is>
           <t>1010</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr"/>
-      <c r="C68" s="2" t="inlineStr"/>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="B68" s="3" t="inlineStr"/>
+      <c r="C68" s="3" t="inlineStr"/>
+      <c r="D68" s="3" t="inlineStr">
         <is>
           <t>Current T phase</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr"/>
+      <c r="E68" s="3" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+      <c r="A69" s="3" t="inlineStr">
         <is>
           <t>1012</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr"/>
-      <c r="C69" s="2" t="inlineStr"/>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="B69" s="3" t="inlineStr"/>
+      <c r="C69" s="3" t="inlineStr"/>
+      <c r="D69" s="3" t="inlineStr">
         <is>
           <t>3 phase effective</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr"/>
+      <c r="E69" s="3" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+      <c r="A70" s="3" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr"/>
-      <c r="C70" s="2" t="inlineStr"/>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="B70" s="3" t="inlineStr"/>
+      <c r="C70" s="3" t="inlineStr"/>
+      <c r="D70" s="3" t="inlineStr">
         <is>
           <t>0.1KW</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr"/>
+      <c r="E70" s="3" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+      <c r="A71" s="3" t="inlineStr">
         <is>
           <t>1014</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr"/>
-      <c r="C71" s="2" t="inlineStr"/>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="B71" s="3" t="inlineStr"/>
+      <c r="C71" s="3" t="inlineStr"/>
+      <c r="D71" s="3" t="inlineStr">
         <is>
           <t>3 phase</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr"/>
+      <c r="E71" s="3" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+      <c r="A72" s="3" t="inlineStr">
         <is>
           <t>1016</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr"/>
-      <c r="C72" s="2" t="inlineStr"/>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="B72" s="3" t="inlineStr"/>
+      <c r="C72" s="3" t="inlineStr"/>
+      <c r="D72" s="3" t="inlineStr">
         <is>
           <t>3 Phase force</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr"/>
+      <c r="E72" s="3" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+      <c r="A73" s="3" t="inlineStr">
         <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr"/>
-      <c r="C73" s="2" t="inlineStr"/>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="B73" s="3" t="inlineStr"/>
+      <c r="C73" s="3" t="inlineStr"/>
+      <c r="D73" s="3" t="inlineStr">
         <is>
           <t>Frequency</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr"/>
+      <c r="E73" s="3" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+      <c r="A74" s="3" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr"/>
-      <c r="C74" s="2" t="inlineStr"/>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="B74" s="3" t="inlineStr"/>
+      <c r="C74" s="3" t="inlineStr"/>
+      <c r="D74" s="3" t="inlineStr">
         <is>
           <t>0.1Hz</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr"/>
+      <c r="E74" s="3" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+      <c r="A75" s="3" t="inlineStr">
         <is>
           <t>1020</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr"/>
-      <c r="C75" s="2" t="inlineStr"/>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="B75" s="3" t="inlineStr"/>
+      <c r="C75" s="3" t="inlineStr"/>
+      <c r="D75" s="3" t="inlineStr">
         <is>
           <t>Status Flag1</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr"/>
+      <c r="E75" s="3" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+      <c r="A76" s="3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr"/>
-      <c r="C76" s="2" t="inlineStr"/>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="B76" s="3" t="inlineStr"/>
+      <c r="C76" s="3" t="inlineStr"/>
+      <c r="D76" s="3" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr"/>
+      <c r="E76" s="3" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+      <c r="A77" s="3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr"/>
-      <c r="C77" s="2" t="inlineStr"/>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="B77" s="3" t="inlineStr"/>
+      <c r="C77" s="3" t="inlineStr"/>
+      <c r="D77" s="3" t="inlineStr">
         <is>
           <t>Working</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr"/>
+      <c r="E77" s="3" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+      <c r="A78" s="3" t="inlineStr">
         <is>
           <t>2001</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr"/>
-      <c r="C78" s="2" t="inlineStr"/>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="B78" s="3" t="inlineStr"/>
+      <c r="C78" s="3" t="inlineStr"/>
+      <c r="D78" s="3" t="inlineStr">
         <is>
           <t>Work and Mode</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr"/>
+      <c r="E78" s="3" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+      <c r="A79" s="3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr"/>
-      <c r="C79" s="2" t="inlineStr"/>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="B79" s="3" t="inlineStr"/>
+      <c r="C79" s="3" t="inlineStr"/>
+      <c r="D79" s="3" t="inlineStr">
         <is>
           <t>0：Separate</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr"/>
+      <c r="E79" s="3" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+      <c r="A80" s="3" t="inlineStr">
         <is>
           <t>2002</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr"/>
-      <c r="C80" s="2" t="inlineStr"/>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="B80" s="3" t="inlineStr"/>
+      <c r="C80" s="3" t="inlineStr"/>
+      <c r="D80" s="3" t="inlineStr">
         <is>
           <t>Constant</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr"/>
+      <c r="E80" s="3" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+      <c r="A81" s="3" t="inlineStr">
         <is>
           <t>2003</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr"/>
-      <c r="C81" s="2" t="inlineStr"/>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="B81" s="3" t="inlineStr"/>
+      <c r="C81" s="3" t="inlineStr"/>
+      <c r="D81" s="3" t="inlineStr">
         <is>
           <t>Constant Active</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr"/>
+      <c r="E81" s="3" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+      <c r="A82" s="3" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr"/>
-      <c r="C82" s="2" t="inlineStr"/>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="B82" s="3" t="inlineStr"/>
+      <c r="C82" s="3" t="inlineStr"/>
+      <c r="D82" s="3" t="inlineStr">
         <is>
           <t>Note：</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr"/>
+      <c r="E82" s="3" t="inlineStr"/>
     </row>
     <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+      <c r="A83" s="3" t="inlineStr">
         <is>
           <t>0x80000000</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr"/>
-      <c r="C83" s="2" t="inlineStr"/>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="B83" s="3" t="inlineStr"/>
+      <c r="C83" s="3" t="inlineStr"/>
+      <c r="D83" s="3" t="inlineStr">
         <is>
           <t>SPI Fail</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr"/>
+      <c r="E83" s="3" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+      <c r="A84" s="3" t="inlineStr">
         <is>
           <t>0x40000000</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr"/>
-      <c r="C84" s="2" t="inlineStr"/>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="B84" s="3" t="inlineStr"/>
+      <c r="C84" s="3" t="inlineStr"/>
+      <c r="D84" s="3" t="inlineStr">
         <is>
           <t>EEPROM R/W Fail</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr"/>
+      <c r="E84" s="3" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+      <c r="A85" s="3" t="inlineStr">
         <is>
           <t>0x20000000</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr"/>
-      <c r="C85" s="2" t="inlineStr"/>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="B85" s="3" t="inlineStr"/>
+      <c r="C85" s="3" t="inlineStr"/>
+      <c r="D85" s="3" t="inlineStr">
         <is>
           <t>Grid frequency overrun</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr"/>
+      <c r="E85" s="3" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+      <c r="A86" s="3" t="inlineStr">
         <is>
           <t>0x10000000</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr"/>
-      <c r="C86" s="2" t="inlineStr"/>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="B86" s="3" t="inlineStr"/>
+      <c r="C86" s="3" t="inlineStr"/>
+      <c r="D86" s="3" t="inlineStr">
         <is>
           <t>AFCI Fault</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr"/>
+      <c r="E86" s="3" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+      <c r="A87" s="3" t="inlineStr">
         <is>
           <t>0x08000000</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr"/>
-      <c r="C87" s="2" t="inlineStr"/>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="B87" s="3" t="inlineStr"/>
+      <c r="C87" s="3" t="inlineStr"/>
+      <c r="D87" s="3" t="inlineStr">
         <is>
           <t>Night SPS Fail</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr"/>
+      <c r="E87" s="3" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+      <c r="A88" s="3" t="inlineStr">
         <is>
           <t>0x04000000</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr"/>
-      <c r="C88" s="2" t="inlineStr"/>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="B88" s="3" t="inlineStr"/>
+      <c r="C88" s="3" t="inlineStr"/>
+      <c r="D88" s="3" t="inlineStr">
         <is>
           <t>L-PE Short Circuit</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr"/>
+      <c r="E88" s="3" t="inlineStr"/>
     </row>
     <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+      <c r="A89" s="3" t="inlineStr">
         <is>
           <t>0x02000000</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr"/>
-      <c r="C89" s="2" t="inlineStr"/>
-      <c r="D89" s="2" t="inlineStr">
+      <c r="B89" s="3" t="inlineStr"/>
+      <c r="C89" s="3" t="inlineStr"/>
+      <c r="D89" s="3" t="inlineStr">
         <is>
           <t>Relay Check Fail</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr"/>
+      <c r="E89" s="3" t="inlineStr"/>
     </row>
     <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+      <c r="A90" s="3" t="inlineStr">
         <is>
           <t>0x01000000</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr"/>
-      <c r="C90" s="2" t="inlineStr"/>
-      <c r="D90" s="2" t="inlineStr">
+      <c r="B90" s="3" t="inlineStr"/>
+      <c r="C90" s="3" t="inlineStr"/>
+      <c r="D90" s="3" t="inlineStr">
         <is>
           <t>N-PE Fail</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr"/>
+      <c r="E90" s="3" t="inlineStr"/>
     </row>
     <row r="91">
-      <c r="A91" s="2" t="inlineStr">
+      <c r="A91" s="3" t="inlineStr">
         <is>
           <t>0x00800000</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr"/>
-      <c r="C91" s="2" t="inlineStr"/>
-      <c r="D91" s="2" t="inlineStr">
+      <c r="B91" s="3" t="inlineStr"/>
+      <c r="C91" s="3" t="inlineStr"/>
+      <c r="D91" s="3" t="inlineStr">
         <is>
           <t>Export Power Limit Fault</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr"/>
+      <c r="E91" s="3" t="inlineStr"/>
     </row>
     <row r="92">
-      <c r="A92" s="2" t="inlineStr">
+      <c r="A92" s="3" t="inlineStr">
         <is>
           <t>0x00400000</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr"/>
-      <c r="C92" s="2" t="inlineStr"/>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="B92" s="3" t="inlineStr"/>
+      <c r="C92" s="3" t="inlineStr"/>
+      <c r="D92" s="3" t="inlineStr">
         <is>
           <t>PV Reverse Fault</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr"/>
+      <c r="E92" s="3" t="inlineStr"/>
     </row>
     <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+      <c r="A93" s="3" t="inlineStr">
         <is>
           <t>0x00200000</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr"/>
-      <c r="C93" s="2" t="inlineStr"/>
-      <c r="D93" s="2" t="inlineStr">
+      <c r="B93" s="3" t="inlineStr"/>
+      <c r="C93" s="3" t="inlineStr"/>
+      <c r="D93" s="3" t="inlineStr">
         <is>
           <t>String Over Current</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr"/>
+      <c r="E93" s="3" t="inlineStr"/>
     </row>
     <row r="94">
-      <c r="A94" s="2" t="inlineStr">
+      <c r="A94" s="3" t="inlineStr">
         <is>
           <t>0x00100000</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr"/>
-      <c r="C94" s="2" t="inlineStr"/>
-      <c r="D94" s="2" t="inlineStr">
+      <c r="B94" s="3" t="inlineStr"/>
+      <c r="C94" s="3" t="inlineStr"/>
+      <c r="D94" s="3" t="inlineStr">
         <is>
           <t>LCD Communication Fail</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr"/>
+      <c r="E94" s="3" t="inlineStr"/>
     </row>
     <row r="95">
-      <c r="A95" s="2" t="inlineStr">
+      <c r="A95" s="3" t="inlineStr">
         <is>
           <t>0x00080000</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr"/>
-      <c r="C95" s="2" t="inlineStr"/>
-      <c r="D95" s="2" t="inlineStr">
+      <c r="B95" s="3" t="inlineStr"/>
+      <c r="C95" s="3" t="inlineStr"/>
+      <c r="D95" s="3" t="inlineStr">
         <is>
           <t>High DC component</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr"/>
+      <c r="E95" s="3" t="inlineStr"/>
     </row>
     <row r="96">
-      <c r="A96" s="2" t="inlineStr">
+      <c r="A96" s="3" t="inlineStr">
         <is>
           <t>0x00040000</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr"/>
-      <c r="C96" s="2" t="inlineStr"/>
-      <c r="D96" s="2" t="inlineStr">
+      <c r="B96" s="3" t="inlineStr"/>
+      <c r="C96" s="3" t="inlineStr"/>
+      <c r="D96" s="3" t="inlineStr">
         <is>
           <t>Isolation Fail</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr"/>
+      <c r="E96" s="3" t="inlineStr"/>
     </row>
     <row r="97">
-      <c r="A97" s="2" t="inlineStr">
+      <c r="A97" s="3" t="inlineStr">
         <is>
           <t>0x00020000</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr"/>
-      <c r="C97" s="2" t="inlineStr"/>
-      <c r="D97" s="2" t="inlineStr">
+      <c r="B97" s="3" t="inlineStr"/>
+      <c r="C97" s="3" t="inlineStr"/>
+      <c r="D97" s="3" t="inlineStr">
         <is>
           <t>Vac Fail (Grid voltage</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr"/>
+      <c r="E97" s="3" t="inlineStr"/>
     </row>
     <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+      <c r="A98" s="3" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr"/>
-      <c r="C98" s="2" t="inlineStr"/>
-      <c r="D98" s="2" t="inlineStr">
+      <c r="B98" s="3" t="inlineStr"/>
+      <c r="C98" s="3" t="inlineStr"/>
+      <c r="D98" s="3" t="inlineStr">
         <is>
           <t>which makes resistance value is high.|4. AC cables are</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr"/>
+      <c r="E98" s="3" t="inlineStr"/>
     </row>
     <row r="99">
-      <c r="A99" s="2" t="inlineStr">
+      <c r="A99" s="3" t="inlineStr">
         <is>
           <t>65536</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr"/>
-      <c r="C99" s="2" t="inlineStr"/>
-      <c r="D99" s="2" t="inlineStr">
+      <c r="B99" s="3" t="inlineStr"/>
+      <c r="C99" s="3" t="inlineStr"/>
+      <c r="D99" s="3" t="inlineStr">
         <is>
           <t>0x00010000</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr"/>
+      <c r="E99" s="3" t="inlineStr"/>
     </row>
     <row r="100">
-      <c r="A100" s="2" t="inlineStr">
+      <c r="A100" s="3" t="inlineStr">
         <is>
           <t>32768</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr"/>
-      <c r="C100" s="2" t="inlineStr"/>
-      <c r="D100" s="2" t="inlineStr">
+      <c r="B100" s="3" t="inlineStr"/>
+      <c r="C100" s="3" t="inlineStr"/>
+      <c r="D100" s="3" t="inlineStr">
         <is>
           <t>0x00008000</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr"/>
+      <c r="E100" s="3" t="inlineStr"/>
     </row>
     <row r="101">
-      <c r="A101" s="2" t="inlineStr">
+      <c r="A101" s="3" t="inlineStr">
         <is>
           <t>16384</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr"/>
-      <c r="C101" s="2" t="inlineStr"/>
-      <c r="D101" s="2" t="inlineStr">
+      <c r="B101" s="3" t="inlineStr"/>
+      <c r="C101" s="3" t="inlineStr"/>
+      <c r="D101" s="3" t="inlineStr">
         <is>
           <t>0x00004000</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr"/>
+      <c r="E101" s="3" t="inlineStr"/>
     </row>
     <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+      <c r="A102" s="3" t="inlineStr">
         <is>
           <t>8192</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr"/>
-      <c r="C102" s="2" t="inlineStr"/>
-      <c r="D102" s="2" t="inlineStr">
+      <c r="B102" s="3" t="inlineStr"/>
+      <c r="C102" s="3" t="inlineStr"/>
+      <c r="D102" s="3" t="inlineStr">
         <is>
           <t>0x00002000</t>
         </is>
       </c>
-      <c r="E102" s="2" t="inlineStr"/>
+      <c r="E102" s="3" t="inlineStr"/>
     </row>
     <row r="103">
-      <c r="A103" s="2" t="inlineStr">
+      <c r="A103" s="3" t="inlineStr">
         <is>
           <t>4096</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr"/>
-      <c r="C103" s="2" t="inlineStr"/>
-      <c r="D103" s="2" t="inlineStr">
+      <c r="B103" s="3" t="inlineStr"/>
+      <c r="C103" s="3" t="inlineStr"/>
+      <c r="D103" s="3" t="inlineStr">
         <is>
           <t>0x00001000</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr"/>
+      <c r="E103" s="3" t="inlineStr"/>
     </row>
     <row r="104">
-      <c r="A104" s="2" t="inlineStr">
+      <c r="A104" s="3" t="inlineStr">
         <is>
           <t>2048</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr"/>
-      <c r="C104" s="2" t="inlineStr"/>
-      <c r="D104" s="2" t="inlineStr">
+      <c r="B104" s="3" t="inlineStr"/>
+      <c r="C104" s="3" t="inlineStr"/>
+      <c r="D104" s="3" t="inlineStr">
         <is>
           <t>0x00000800</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr"/>
+      <c r="E104" s="3" t="inlineStr"/>
     </row>
     <row r="105">
-      <c r="A105" s="2" t="inlineStr">
+      <c r="A105" s="3" t="inlineStr">
         <is>
           <t>1024</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr"/>
-      <c r="C105" s="2" t="inlineStr"/>
-      <c r="D105" s="2" t="inlineStr">
+      <c r="B105" s="3" t="inlineStr"/>
+      <c r="C105" s="3" t="inlineStr"/>
+      <c r="D105" s="3" t="inlineStr">
         <is>
           <t>0x00000400</t>
         </is>
       </c>
-      <c r="E105" s="2" t="inlineStr"/>
+      <c r="E105" s="3" t="inlineStr"/>
     </row>
     <row r="106">
-      <c r="A106" s="2" t="inlineStr">
+      <c r="A106" s="3" t="inlineStr">
         <is>
           <t>512</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr"/>
-      <c r="C106" s="2" t="inlineStr"/>
-      <c r="D106" s="2" t="inlineStr">
+      <c r="B106" s="3" t="inlineStr"/>
+      <c r="C106" s="3" t="inlineStr"/>
+      <c r="D106" s="3" t="inlineStr">
         <is>
           <t>0x00000200</t>
         </is>
       </c>
-      <c r="E106" s="2" t="inlineStr"/>
+      <c r="E106" s="3" t="inlineStr"/>
     </row>
     <row r="107">
-      <c r="A107" s="2" t="inlineStr">
+      <c r="A107" s="3" t="inlineStr">
         <is>
           <t>256</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr"/>
-      <c r="C107" s="2" t="inlineStr"/>
-      <c r="D107" s="2" t="inlineStr">
+      <c r="B107" s="3" t="inlineStr"/>
+      <c r="C107" s="3" t="inlineStr"/>
+      <c r="D107" s="3" t="inlineStr">
         <is>
           <t>0x00000100</t>
         </is>
       </c>
-      <c r="E107" s="2" t="inlineStr"/>
+      <c r="E107" s="3" t="inlineStr"/>
     </row>
     <row r="108">
-      <c r="A108" s="2" t="inlineStr">
+      <c r="A108" s="3" t="inlineStr">
         <is>
           <t>128</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr"/>
-      <c r="C108" s="2" t="inlineStr"/>
-      <c r="D108" s="2" t="inlineStr">
+      <c r="B108" s="3" t="inlineStr"/>
+      <c r="C108" s="3" t="inlineStr"/>
+      <c r="D108" s="3" t="inlineStr">
         <is>
           <t>0x00000080</t>
         </is>
       </c>
-      <c r="E108" s="2" t="inlineStr"/>
+      <c r="E108" s="3" t="inlineStr"/>
     </row>
     <row r="109">
-      <c r="A109" s="2" t="inlineStr">
+      <c r="A109" s="3" t="inlineStr">
         <is>
           <t>64</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr"/>
-      <c r="C109" s="2" t="inlineStr"/>
-      <c r="D109" s="2" t="inlineStr">
+      <c r="B109" s="3" t="inlineStr"/>
+      <c r="C109" s="3" t="inlineStr"/>
+      <c r="D109" s="3" t="inlineStr">
         <is>
           <t>0x00000040</t>
         </is>
       </c>
-      <c r="E109" s="2" t="inlineStr"/>
+      <c r="E109" s="3" t="inlineStr"/>
     </row>
     <row r="110">
-      <c r="A110" s="2" t="inlineStr">
+      <c r="A110" s="3" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr"/>
-      <c r="C110" s="2" t="inlineStr"/>
-      <c r="D110" s="2" t="inlineStr">
+      <c r="B110" s="3" t="inlineStr"/>
+      <c r="C110" s="3" t="inlineStr"/>
+      <c r="D110" s="3" t="inlineStr">
         <is>
           <t>0x00000020</t>
         </is>
       </c>
-      <c r="E110" s="2" t="inlineStr"/>
+      <c r="E110" s="3" t="inlineStr"/>
     </row>
     <row r="111">
-      <c r="A111" s="2" t="inlineStr">
+      <c r="A111" s="3" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr"/>
-      <c r="C111" s="2" t="inlineStr"/>
-      <c r="D111" s="2" t="inlineStr">
+      <c r="B111" s="3" t="inlineStr"/>
+      <c r="C111" s="3" t="inlineStr"/>
+      <c r="D111" s="3" t="inlineStr">
         <is>
           <t>0x00000010</t>
         </is>
       </c>
-      <c r="E111" s="2" t="inlineStr"/>
+      <c r="E111" s="3" t="inlineStr"/>
     </row>
     <row r="112">
-      <c r="A112" s="2" t="inlineStr">
+      <c r="A112" s="3" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr"/>
-      <c r="C112" s="2" t="inlineStr"/>
-      <c r="D112" s="2" t="inlineStr">
+      <c r="B112" s="3" t="inlineStr"/>
+      <c r="C112" s="3" t="inlineStr"/>
+      <c r="D112" s="3" t="inlineStr">
         <is>
           <t>0x00000008</t>
         </is>
       </c>
-      <c r="E112" s="2" t="inlineStr"/>
+      <c r="E112" s="3" t="inlineStr"/>
     </row>
     <row r="113">
-      <c r="A113" s="2" t="inlineStr">
+      <c r="A113" s="3" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr"/>
-      <c r="C113" s="2" t="inlineStr"/>
-      <c r="D113" s="2" t="inlineStr">
+      <c r="B113" s="3" t="inlineStr"/>
+      <c r="C113" s="3" t="inlineStr"/>
+      <c r="D113" s="3" t="inlineStr">
         <is>
           <t>0x00000004</t>
         </is>
       </c>
-      <c r="E113" s="2" t="inlineStr"/>
+      <c r="E113" s="3" t="inlineStr"/>
     </row>
     <row r="114">
-      <c r="A114" s="2" t="inlineStr">
+      <c r="A114" s="3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr"/>
-      <c r="C114" s="2" t="inlineStr"/>
-      <c r="D114" s="2" t="inlineStr">
+      <c r="B114" s="3" t="inlineStr"/>
+      <c r="C114" s="3" t="inlineStr"/>
+      <c r="D114" s="3" t="inlineStr">
         <is>
           <t>0x00000002</t>
         </is>
       </c>
-      <c r="E114" s="2" t="inlineStr"/>
+      <c r="E114" s="3" t="inlineStr"/>
     </row>
     <row r="115">
-      <c r="A115" s="2" t="inlineStr">
+      <c r="A115" s="3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr"/>
-      <c r="C115" s="2" t="inlineStr"/>
-      <c r="D115" s="2" t="inlineStr">
+      <c r="B115" s="3" t="inlineStr"/>
+      <c r="C115" s="3" t="inlineStr"/>
+      <c r="D115" s="3" t="inlineStr">
         <is>
           <t>0x00000001</t>
         </is>
       </c>
-      <c r="E115" s="2" t="inlineStr"/>
+      <c r="E115" s="3" t="inlineStr"/>
     </row>
     <row r="116">
-      <c r="A116" s="2" t="inlineStr">
+      <c r="A116" s="3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr"/>
-      <c r="C116" s="2" t="inlineStr"/>
-      <c r="D116" s="2" t="inlineStr">
+      <c r="B116" s="3" t="inlineStr"/>
+      <c r="C116" s="3" t="inlineStr"/>
+      <c r="D116" s="3" t="inlineStr">
         <is>
           <t>Bit15</t>
         </is>
       </c>
-      <c r="E116" s="2" t="inlineStr"/>
+      <c r="E116" s="3" t="inlineStr"/>
     </row>
     <row r="117">
-      <c r="A117" s="2" t="inlineStr">
+      <c r="A117" s="3" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr"/>
-      <c r="C117" s="2" t="inlineStr"/>
-      <c r="D117" s="2" t="inlineStr">
+      <c r="B117" s="3" t="inlineStr"/>
+      <c r="C117" s="3" t="inlineStr"/>
+      <c r="D117" s="3" t="inlineStr">
         <is>
           <t>Bit12</t>
         </is>
       </c>
-      <c r="E117" s="2" t="inlineStr"/>
+      <c r="E117" s="3" t="inlineStr"/>
     </row>
     <row r="118">
-      <c r="A118" s="2" t="inlineStr">
+      <c r="A118" s="3" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr"/>
-      <c r="C118" s="2" t="inlineStr"/>
-      <c r="D118" s="2" t="inlineStr">
+      <c r="B118" s="3" t="inlineStr"/>
+      <c r="C118" s="3" t="inlineStr"/>
+      <c r="D118" s="3" t="inlineStr">
         <is>
           <t>Bit15</t>
         </is>
       </c>
-      <c r="E118" s="2" t="inlineStr"/>
+      <c r="E118" s="3" t="inlineStr"/>
     </row>
     <row r="119">
-      <c r="A119" s="2" t="inlineStr">
+      <c r="A119" s="3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr"/>
-      <c r="C119" s="2" t="inlineStr"/>
-      <c r="D119" s="2" t="inlineStr">
+      <c r="B119" s="3" t="inlineStr"/>
+      <c r="C119" s="3" t="inlineStr"/>
+      <c r="D119" s="3" t="inlineStr">
         <is>
           <t>Set : Stop, Reset : Work</t>
         </is>
       </c>
-      <c r="E119" s="2" t="inlineStr"/>
+      <c r="E119" s="3" t="inlineStr"/>
     </row>
     <row r="120">
-      <c r="A120" s="2" t="inlineStr">
+      <c r="A120" s="3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr"/>
-      <c r="C120" s="2" t="inlineStr"/>
-      <c r="D120" s="2" t="inlineStr">
+      <c r="B120" s="3" t="inlineStr"/>
+      <c r="C120" s="3" t="inlineStr"/>
+      <c r="D120" s="3" t="inlineStr">
         <is>
           <t>Set : Fail, Reset : Normal</t>
         </is>
       </c>
-      <c r="E120" s="2" t="inlineStr"/>
+      <c r="E120" s="3" t="inlineStr"/>
     </row>
     <row r="121">
-      <c r="A121" s="2" t="inlineStr">
+      <c r="A121" s="3" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr"/>
-      <c r="C121" s="2" t="inlineStr"/>
-      <c r="D121" s="2" t="inlineStr">
+      <c r="B121" s="3" t="inlineStr"/>
+      <c r="C121" s="3" t="inlineStr"/>
+      <c r="D121" s="3" t="inlineStr">
         <is>
           <t>Set : Separate, Reset : Contact 1</t>
         </is>
       </c>
-      <c r="E121" s="2" t="inlineStr"/>
+      <c r="E121" s="3" t="inlineStr"/>
     </row>
     <row r="122">
-      <c r="A122" s="2" t="inlineStr">
+      <c r="A122" s="3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr"/>
-      <c r="C122" s="2" t="inlineStr"/>
-      <c r="D122" s="2" t="inlineStr">
+      <c r="B122" s="3" t="inlineStr"/>
+      <c r="C122" s="3" t="inlineStr"/>
+      <c r="D122" s="3" t="inlineStr">
         <is>
           <t>Separate operation</t>
         </is>
       </c>
-      <c r="E122" s="2" t="inlineStr"/>
+      <c r="E122" s="3" t="inlineStr"/>
     </row>
     <row r="123">
-      <c r="A123" s="2" t="inlineStr">
+      <c r="A123" s="3" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr"/>
-      <c r="C123" s="2" t="inlineStr"/>
-      <c r="D123" s="2" t="inlineStr">
+      <c r="B123" s="3" t="inlineStr"/>
+      <c r="C123" s="3" t="inlineStr"/>
+      <c r="D123" s="3" t="inlineStr">
         <is>
           <t>9. Example</t>
         </is>
       </c>
-      <c r="E123" s="2" t="inlineStr"/>
+      <c r="E123" s="3" t="inlineStr"/>
     </row>
     <row r="124">
-      <c r="A124" s="2" t="inlineStr">
+      <c r="A124" s="3" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr"/>
-      <c r="C124" s="2" t="inlineStr"/>
-      <c r="D124" s="2" t="inlineStr">
+      <c r="B124" s="3" t="inlineStr"/>
+      <c r="C124" s="3" t="inlineStr"/>
+      <c r="D124" s="3" t="inlineStr">
         <is>
           <t>Device Return</t>
         </is>
       </c>
-      <c r="E124" s="2" t="inlineStr"/>
+      <c r="E124" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
